--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
-          <t>ESTIMATE, range 3 to 6% of TPV. Anchors: dLocal FY2025 revenue / TPV = 2.68% (2.92% in 2024), a blended figure across pay-ins, pay-outs and very large merchants, so a floor for a $0.5 to 4.5M a month digital-goods merchant (FXC Intelligence, 26 Mar 2026, on dLocal's results of 18 Mar 2026). EBANX reviewer: about 5% per transaction plus a $200 monthly fee (Capterra, Nov 2021). FX spread of 1 to 3% on top of processing (Nuvei, 2026). Brazil IOF on FX 3.5% (Decree 12,466/2025, PayPro Global).</t>
+          <t>ESTIMATE, range 3 to 6% of TPV. Anchors: dLocal FY2025 revenue / TPV = 2.68% (2.92% in 2024), a blended figure across pay-ins, pay-outs and very large merchants, so a low anchor for a $0.5 to 4.5M a month digital-goods merchant (FXC Intelligence, 26 Mar 2026, on dLocal's results of 18 Mar 2026). EBANX reviewer: about 5% per transaction plus a $200 monthly fee (Capterra, Nov 2021). FX spread of 1 to 3% on top of processing (Nuvei, 2026). Brazil IOF on FX 3.5% (Decree 12,466/2025, PayPro Global).</t>
         </is>
       </c>
       <c r="H16" s="28" t="inlineStr">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Annual maintenance, % of build cost per integration</t>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G30" s="28" t="inlineStr">
         <is>
-          <t>Yuno estimate; 20 to 30% upkeep is the convention used in Yuno business cases (Luni, Oct 2026).</t>
+          <t>Yuno estimate; 20 to 30% upkeep is the convention used in Yuno business cases (Oct 2026).</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 · monthly TPV up to</t>
+          <t>Tranche 1 · monthly TPV ceiling</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 · monthly TPV up to</t>
+          <t>Tranche 2 · monthly TPV ceiling</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 · TPV up to</t>
+          <t>Tranche 1 · TPV ceiling</t>
         </is>
       </c>
       <c r="B7" s="44">
@@ -2449,7 +2449,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 · TPV up to</t>
+          <t>Tranche 2 · TPV ceiling</t>
         </is>
       </c>
       <c r="B9" s="44">

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -254,14 +254,14 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>TPV a month</t>
+          <t>Net TPV a month</t>
         </is>
       </c>
       <c r="D8" s="9">
@@ -1149,7 +1149,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>How to read: Option A = EBANX direct at the baseline all-in cost (ESTIMATE until EBANX's quote replaces Inputs row for the baseline). Option B = EBANX primary + dLocal second MoR through Yuno; its provider cost is the baseline minus the MDR reduction, plus Yuno's platform fee and usage. Levers: L1 MDR saving (100% contribution), L2 retries and routing, L3 local methods, L4 engineering saved. Contribution view nets the take rate and processing cost on incremental GMV. Yuno-wide figures used only as guardrails: 7% authorization uplift, 30% recovered revenue (y.uno).</t>
+          <t>How to read: Option A = EBANX direct at the baseline all-in cost (ESTIMATE until EBANX's quote replaces the baseline on Inputs). Option B = EBANX primary + dLocal second MoR through Yuno; its provider cost is the baseline minus the MDR reduction, plus Yuno's flat platform fee and usage in bps on the Net TPV above the included block. Levers: L1 MDR saving (100% contribution), L2 retries and routing, L3 local methods, L4 engineering saved. Contribution view nets the take rate and processing cost on incremental GMV. Yuno-wide figures used only as guardrails: 7% authorization uplift, 30% recovered revenue (y.uno).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1991,7 +1991,7 @@
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>7 · Yuno cost line (the proposal)</t>
+          <t>7 · Yuno cost line (the proposal, pricing v3: bps on monthly Net TPV)</t>
         </is>
       </c>
       <c r="C32" s="25" t="n"/>
@@ -2004,7 +2004,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Platform fee a month</t>
+          <t>Platform fee a month (flat)</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>Justo Benetti, 15 Oct 2026: $7.5K a month platform commitment with a block of transactions included.</t>
+          <t>Justo Benetti, 15 Oct 2026: $7,500 a month flat platform fee that includes a block of monthly Net TPV. Net TPV = successful transactions only, no declines, no chargebacks.</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
@@ -2037,28 +2037,28 @@
     <row r="34" ht="45" customHeight="1">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Successful transactions included in the platform fee each month</t>
+          <t>Monthly Net TPV included in the platform fee (single month, no rollover)</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>tx</t>
-        </is>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E34" s="30">
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E34" s="11">
         <f>D34</f>
         <v/>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="11">
         <f>D34</f>
         <v/>
       </c>
       <c r="G34" s="28" t="inlineStr">
         <is>
-          <t>Proposal: equals the launch tier, so at 50K a month Carry1st pays the platform fee and nothing else. Billable TPV = TPV x max(0, 1 minus N / transactions), i.e. the TPV of the transactions above the block at the month's average ticket.</t>
+          <t>Pricing v3, German's decision, 15 Oct 2026. Justo's rule: pay-ins are billed in bps on TPV, so the included block is in TPV, never in transactions (units must match). At a $10 ticket this block is about 50,000 transactions; at $5, about 100,000.</t>
         </is>
       </c>
       <c r="H34" s="28" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 · monthly TPV ceiling</t>
+          <t>Tranche 1 · monthly Net TPV ceiling</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D35" s="40" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="E35" s="11">
         <f>D35</f>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G35" s="28" t="inlineStr">
         <is>
-          <t>Proposal (ladder: each tranche applies only to the TPV inside it).</t>
+          <t>Proposal (ladder: each tranche applies only to the Net TPV inside it).</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 · usage rate, % of billable TPV</t>
+          <t>Tranche 1 · usage rate on Net TPV above the included block</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D36" s="37" t="n">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="E36" s="36">
         <f>D36</f>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G36" s="28" t="inlineStr">
         <is>
-          <t>Proposal. At a $10 ticket this is $0.045 per successful transaction; at $5, $0.0225.</t>
+          <t>Proposal: 30 bps. At a $10 ticket this is $0.030 per successful transaction; at $5, $0.015.</t>
         </is>
       </c>
       <c r="H36" s="28" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 · monthly TPV ceiling</t>
+          <t>Tranche 2 · monthly Net TPV ceiling</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="D37" s="40" t="n">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="E37" s="11">
         <f>D37</f>
@@ -2169,7 +2169,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 · usage rate, % of billable TPV</t>
+          <t>Tranche 2 · usage rate</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="D38" s="37" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="E38" s="36">
         <f>D38</f>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G38" s="28" t="inlineStr">
         <is>
-          <t>Proposal. $0.035 per transaction at a $10 ticket.</t>
+          <t>Proposal: 25 bps. $0.025 per transaction at a $10 ticket; $0.0125 at $5.</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -2202,7 +2202,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Tranche 3 · usage rate above tranche 2, % of billable TPV</t>
+          <t>Tranche 3 · usage rate above tranche 2</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D39" s="37" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E39" s="36">
         <f>D39</f>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G39" s="28" t="inlineStr">
         <is>
-          <t>Proposal. $0.030 per transaction at a $10 ticket.</t>
+          <t>Proposal: 20 bps. $0.020 per transaction at a $10 ticket; $0.010 at $5.</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -2336,15 +2336,127 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="43" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>9 · INTERNAL launch lever (switch, default 0 = off; delete this section before the file leaves Yuno)</t>
+        </is>
+      </c>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Launch credit switch (1 = on, 0 = off)</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="34">
+        <f>D45</f>
+        <v/>
+      </c>
+      <c r="F45" s="34">
+        <f>D45</f>
+        <v/>
+      </c>
+      <c r="G45" s="28" t="inlineStr">
+        <is>
+          <t>INTERNAL. Optional lever: a monthly credit against the platform fee for the first months after the 1 Dec 2026 billing start. Applies on the Ramp sheet only. Never on the customer slide.</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="inlineStr">
+        <is>
+          <t>Justo · Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Monthly credit against the platform fee when the switch is on</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E46" s="11">
+        <f>D46</f>
+        <v/>
+      </c>
+      <c r="F46" s="11">
+        <f>D46</f>
+        <v/>
+      </c>
+      <c r="G46" s="28" t="inlineStr">
+        <is>
+          <t>INTERNAL. Credits are allowed against the platform fee only, for named months, written in the contract, no rollover.</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="inlineStr">
+        <is>
+          <t>Justo · Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Months the credit applies (from the billing start)</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="34">
+        <f>D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="34">
+        <f>D47</f>
+        <v/>
+      </c>
+      <c r="G47" s="28" t="inlineStr">
+        <is>
+          <t>INTERNAL. Dec 2026 to Feb 2027.</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="inlineStr">
+        <is>
+          <t>Justo · Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>Published Yuno figures used as guardrails only (never as inputs): 7% authorization uplift and 30% recovered revenue (y.uno). Treat 7% as the ceiling for the optimistic case.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="43" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>Labels: CONFIRMED (docs.y.uno or y.uno) · PUBLIC DOCS (third-party page, dated) · OPEN (not confirmed in writing, with owner) · ESTIMATE (modeled; assumption stated) · Carry1st estimate (Cordel, Oct 2026).</t>
         </is>
@@ -2365,10 +2477,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2383,14 +2495,14 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pricing · Yuno proposal: $7,500 a month with a block of transactions included, usage above as % of TPV in tranches</t>
+          <t>Pricing · Yuno proposal: $7,500 a month flat including the first block of monthly Net TPV, usage above it in bps on Net TPV (ladder)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Billable event = successful transaction. Declines are not billed. Each tranche applies only to the TPV inside it. Add-ons (network tokens, 3DS) billed on usage and not in these totals.</t>
+          <t>Billable event = successful transaction. Net TPV = successful transactions only, no declines, no chargebacks. Each tranche applies only to the Net TPV inside it. Add-ons (network tokens, 3DS) billed on usage and not in these totals.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2517,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Platform fee a month</t>
+          <t>Platform fee a month (flat)</t>
         </is>
       </c>
       <c r="B5" s="44">
@@ -2416,10 +2528,10 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Successful transactions included each month</t>
-        </is>
-      </c>
-      <c r="B6" s="45">
+          <t>Monthly Net TPV included in the platform fee</t>
+        </is>
+      </c>
+      <c r="B6" s="44">
         <f>Inputs!$E$34</f>
         <v/>
       </c>
@@ -2427,7 +2539,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 · TPV ceiling</t>
+          <t>Tranche 1 · Net TPV ceiling</t>
         </is>
       </c>
       <c r="B7" s="44">
@@ -2441,7 +2553,7 @@
           <t>Tranche 1 · rate</t>
         </is>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="45">
         <f>Inputs!$E$36</f>
         <v/>
       </c>
@@ -2449,7 +2561,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 · TPV ceiling</t>
+          <t>Tranche 2 · Net TPV ceiling</t>
         </is>
       </c>
       <c r="B9" s="44">
@@ -2463,7 +2575,7 @@
           <t>Tranche 2 · rate</t>
         </is>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="45">
         <f>Inputs!$E$38</f>
         <v/>
       </c>
@@ -2474,7 +2586,7 @@
           <t>Tranche 3 · rate above tranche 2</t>
         </is>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="45">
         <f>Inputs!$E$39</f>
         <v/>
       </c>
@@ -2482,118 +2594,106 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 rate, $ per transaction at the average ticket</t>
-        </is>
-      </c>
-      <c r="B12" s="47">
-        <f>Inputs!$E$36*Inputs!$E$6</f>
+          <t>Included block, transactions at the average ticket</t>
+        </is>
+      </c>
+      <c r="B12" s="46">
+        <f>Inputs!$E$34/Inputs!$E$6</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 rate, $ per transaction at the average ticket</t>
+          <t>Tranche 1 rate, $ per transaction at the average ticket</t>
         </is>
       </c>
       <c r="B13" s="47">
-        <f>Inputs!$E$38*Inputs!$E$6</f>
+        <f>Inputs!$E$36*Inputs!$E$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Tranche 3 rate, $ per transaction at the average ticket</t>
+          <t>Tranche 2 rate, $ per transaction at the average ticket</t>
         </is>
       </c>
       <c r="B14" s="47">
-        <f>Inputs!$E$39*Inputs!$E$6</f>
+        <f>Inputs!$E$38*Inputs!$E$6</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Tranche 1 rate, $ per transaction at the median ticket</t>
+          <t>Tranche 3 rate, $ per transaction at the average ticket</t>
         </is>
       </c>
       <c r="B15" s="47">
-        <f>Inputs!$E$36*Inputs!$E$7</f>
+        <f>Inputs!$E$39*Inputs!$E$6</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Tranche 2 rate, $ per transaction at the median ticket</t>
+          <t>Tranche 1 rate, $ per transaction at the median ticket</t>
         </is>
       </c>
       <c r="B16" s="47">
-        <f>Inputs!$E$38*Inputs!$E$7</f>
+        <f>Inputs!$E$36*Inputs!$E$7</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>Tranche 2 rate, $ per transaction at the median ticket</t>
+        </is>
+      </c>
+      <c r="B17" s="47">
+        <f>Inputs!$E$38*Inputs!$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>Tranche 3 rate, $ per transaction at the median ticket</t>
         </is>
       </c>
-      <c r="B17" s="47">
+      <c r="B18" s="47">
         <f>Inputs!$E$39*Inputs!$E$7</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>What it means for Carry1st at the AVERAGE ticket ($10)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="7">
         <f>Inputs!$E$8</f>
         <v/>
       </c>
-      <c r="C20" s="7">
+      <c r="C21" s="7">
         <f>Inputs!$E$9</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="7">
         <f>Inputs!$E$10</f>
         <v/>
       </c>
-      <c r="E20" s="7">
-        <f>Inputs!$E$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Successful transactions a month</t>
-        </is>
-      </c>
-      <c r="B21" s="30">
-        <f>Inputs!$E$8</f>
-        <v/>
-      </c>
-      <c r="C21" s="30">
-        <f>Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="D21" s="30">
-        <f>Inputs!$E$10</f>
-        <v/>
-      </c>
-      <c r="E21" s="30">
+      <c r="E21" s="7">
         <f>Inputs!$E$11</f>
         <v/>
       </c>
@@ -2601,443 +2701,443 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>TPV a month</t>
-        </is>
-      </c>
-      <c r="B22" s="9">
-        <f>B21*Inputs!$E$6</f>
-        <v/>
-      </c>
-      <c r="C22" s="9">
-        <f>C21*Inputs!$E$6</f>
-        <v/>
-      </c>
-      <c r="D22" s="9">
-        <f>D21*Inputs!$E$6</f>
-        <v/>
-      </c>
-      <c r="E22" s="9">
-        <f>E21*Inputs!$E$6</f>
+          <t>Successful transactions a month</t>
+        </is>
+      </c>
+      <c r="B22" s="48">
+        <f>Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C22" s="48">
+        <f>Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D22" s="48">
+        <f>Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E22" s="48">
+        <f>Inputs!$E$11</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>TPV inside the included block</t>
+          <t>Net TPV a month</t>
         </is>
       </c>
       <c r="B23" s="11">
-        <f>MIN(B21,Inputs!$E$34)*B22/B21</f>
+        <f>B22*Inputs!$E$6</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>MIN(C21,Inputs!$E$34)*C22/C21</f>
+        <f>C22*Inputs!$E$6</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>MIN(D21,Inputs!$E$34)*D22/D21</f>
+        <f>D22*Inputs!$E$6</f>
         <v/>
       </c>
       <c r="E23" s="11">
-        <f>MIN(E21,Inputs!$E$34)*E22/E21</f>
+        <f>E22*Inputs!$E$6</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 1</t>
+          <t>Net TPV inside the included block</t>
         </is>
       </c>
       <c r="B24" s="9">
-        <f>MAX(0,MIN(B22,Inputs!$E$35)-MAX(0,B23))</f>
+        <f>MIN(B23,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="C24" s="9">
-        <f>MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,C23))</f>
+        <f>MIN(C23,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D24" s="9">
-        <f>MAX(0,MIN(D22,Inputs!$E$35)-MAX(0,D23))</f>
+        <f>MIN(D23,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="E24" s="9">
-        <f>MAX(0,MIN(E22,Inputs!$E$35)-MAX(0,E23))</f>
+        <f>MIN(E23,Inputs!$E$34)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 2</t>
+          <t>Billable Net TPV · tranche 1</t>
         </is>
       </c>
       <c r="B25" s="11">
-        <f>MAX(0,MIN(B22,Inputs!$E$37)-MAX(Inputs!$E$35,B23))</f>
+        <f>MAX(0,MIN(B23,Inputs!$E$35)-MAX(0,B24))</f>
         <v/>
       </c>
       <c r="C25" s="11">
-        <f>MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,C23))</f>
+        <f>MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,C24))</f>
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>MAX(0,MIN(D22,Inputs!$E$37)-MAX(Inputs!$E$35,D23))</f>
+        <f>MAX(0,MIN(D23,Inputs!$E$35)-MAX(0,D24))</f>
         <v/>
       </c>
       <c r="E25" s="11">
-        <f>MAX(0,MIN(E22,Inputs!$E$37)-MAX(Inputs!$E$35,E23))</f>
+        <f>MAX(0,MIN(E23,Inputs!$E$35)-MAX(0,E24))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 3</t>
+          <t>Billable Net TPV · tranche 2</t>
         </is>
       </c>
       <c r="B26" s="9">
-        <f>MAX(0,B22-MAX(Inputs!$E$37,B23))</f>
+        <f>MAX(0,MIN(B23,Inputs!$E$37)-MAX(Inputs!$E$35,B24))</f>
         <v/>
       </c>
       <c r="C26" s="9">
-        <f>MAX(0,C22-MAX(Inputs!$E$37,C23))</f>
+        <f>MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,C24))</f>
         <v/>
       </c>
       <c r="D26" s="9">
-        <f>MAX(0,D22-MAX(Inputs!$E$37,D23))</f>
+        <f>MAX(0,MIN(D23,Inputs!$E$37)-MAX(Inputs!$E$35,D24))</f>
         <v/>
       </c>
       <c r="E26" s="9">
-        <f>MAX(0,E22-MAX(Inputs!$E$37,E23))</f>
+        <f>MAX(0,MIN(E23,Inputs!$E$37)-MAX(Inputs!$E$35,E24))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Usage fee</t>
+          <t>Billable Net TPV · tranche 3</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>B24*Inputs!$E$36+B25*Inputs!$E$38+B26*Inputs!$E$39</f>
+        <f>MAX(0,B23-MAX(Inputs!$E$37,B24))</f>
         <v/>
       </c>
       <c r="C27" s="11">
-        <f>C24*Inputs!$E$36+C25*Inputs!$E$38+C26*Inputs!$E$39</f>
+        <f>MAX(0,C23-MAX(Inputs!$E$37,C24))</f>
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>D24*Inputs!$E$36+D25*Inputs!$E$38+D26*Inputs!$E$39</f>
+        <f>MAX(0,D23-MAX(Inputs!$E$37,D24))</f>
         <v/>
       </c>
       <c r="E27" s="11">
-        <f>E24*Inputs!$E$36+E25*Inputs!$E$38+E26*Inputs!$E$39</f>
+        <f>MAX(0,E23-MAX(Inputs!$E$37,E24))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
+          <t>Usage fee</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>B25*Inputs!$E$36+B26*Inputs!$E$38+B27*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="C28" s="9">
+        <f>C25*Inputs!$E$36+C26*Inputs!$E$38+C27*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>D25*Inputs!$E$36+D26*Inputs!$E$38+D27*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
+        <f>E25*Inputs!$E$36+E26*Inputs!$E$38+E27*Inputs!$E$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
           <t>Platform fee</t>
         </is>
       </c>
-      <c r="B28" s="9">
+      <c r="B29" s="11">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="C28" s="9">
+      <c r="C29" s="11">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="D28" s="9">
+      <c r="D29" s="11">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="E28" s="9">
+      <c r="E29" s="11">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Yuno total a month</t>
         </is>
       </c>
-      <c r="B29" s="16">
-        <f>B27+B28</f>
-        <v/>
-      </c>
-      <c r="C29" s="16">
-        <f>C27+C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="16">
-        <f>D27+D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>E27+E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B30" s="18">
+        <f>B28+B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="18">
+        <f>C28+C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>D28+D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f>E28+E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Yuno total a year</t>
         </is>
       </c>
-      <c r="B30" s="9">
-        <f>B29*12</f>
-        <v/>
-      </c>
-      <c r="C30" s="9">
-        <f>C29*12</f>
-        <v/>
-      </c>
-      <c r="D30" s="9">
-        <f>D29*12</f>
-        <v/>
-      </c>
-      <c r="E30" s="9">
-        <f>E29*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Yuno cost, % of TPV</t>
-        </is>
-      </c>
-      <c r="B31" s="48">
-        <f>B29/B22</f>
-        <v/>
-      </c>
-      <c r="C31" s="48">
-        <f>C29/C22</f>
-        <v/>
-      </c>
-      <c r="D31" s="48">
-        <f>D29/D22</f>
-        <v/>
-      </c>
-      <c r="E31" s="48">
-        <f>E29/E22</f>
+      <c r="B31" s="11">
+        <f>B30*12</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>C30*12</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>D30*12</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>E30*12</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>Yuno cost, % of TPV</t>
+        </is>
+      </c>
+      <c r="B32" s="49">
+        <f>B30/B23</f>
+        <v/>
+      </c>
+      <c r="C32" s="49">
+        <f>C30/C23</f>
+        <v/>
+      </c>
+      <c r="D32" s="49">
+        <f>D30/D23</f>
+        <v/>
+      </c>
+      <c r="E32" s="49">
+        <f>E30/E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>Yuno cost per successful transaction</t>
         </is>
       </c>
-      <c r="B32" s="49">
-        <f>B29/B21</f>
-        <v/>
-      </c>
-      <c r="C32" s="49">
-        <f>C29/C21</f>
-        <v/>
-      </c>
-      <c r="D32" s="49">
-        <f>D29/D21</f>
-        <v/>
-      </c>
-      <c r="E32" s="49">
-        <f>E29/E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Hypothetical fixed fee A a month (comparison)</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
-        <f>B21*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="C33" s="11">
-        <f>C21*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="D33" s="11">
-        <f>D21*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="E33" s="11">
-        <f>E21*Inputs!$E$40</f>
+      <c r="B33" s="50">
+        <f>B30/B22</f>
+        <v/>
+      </c>
+      <c r="C33" s="50">
+        <f>C30/C22</f>
+        <v/>
+      </c>
+      <c r="D33" s="50">
+        <f>D30/D22</f>
+        <v/>
+      </c>
+      <c r="E33" s="50">
+        <f>E30/E22</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Fixed fee A, % of TPV</t>
-        </is>
-      </c>
-      <c r="B34" s="12">
-        <f>B33/B22</f>
-        <v/>
-      </c>
-      <c r="C34" s="12">
-        <f>C33/C22</f>
-        <v/>
-      </c>
-      <c r="D34" s="12">
-        <f>D33/D22</f>
-        <v/>
-      </c>
-      <c r="E34" s="12">
-        <f>E33/E22</f>
+          <t>Hypothetical fixed fee A a month (comparison)</t>
+        </is>
+      </c>
+      <c r="B34" s="9">
+        <f>B22*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="C34" s="9">
+        <f>C22*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="D34" s="9">
+        <f>D22*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="E34" s="9">
+        <f>E22*Inputs!$E$40</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Hypothetical fixed fee B a month (comparison)</t>
-        </is>
-      </c>
-      <c r="B35" s="11">
-        <f>B21*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>C21*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="D35" s="11">
-        <f>D21*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="E35" s="11">
-        <f>E21*Inputs!$E$41</f>
+          <t>Fixed fee A, % of TPV</t>
+        </is>
+      </c>
+      <c r="B35" s="36">
+        <f>B34/B23</f>
+        <v/>
+      </c>
+      <c r="C35" s="36">
+        <f>C34/C23</f>
+        <v/>
+      </c>
+      <c r="D35" s="36">
+        <f>D34/D23</f>
+        <v/>
+      </c>
+      <c r="E35" s="36">
+        <f>E34/E23</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Fixed fee B, % of TPV</t>
-        </is>
-      </c>
-      <c r="B36" s="12">
-        <f>B35/B22</f>
-        <v/>
-      </c>
-      <c r="C36" s="12">
-        <f>C35/C22</f>
-        <v/>
-      </c>
-      <c r="D36" s="12">
-        <f>D35/D22</f>
-        <v/>
-      </c>
-      <c r="E36" s="12">
-        <f>E35/E22</f>
+          <t>Hypothetical fixed fee B a month (comparison)</t>
+        </is>
+      </c>
+      <c r="B36" s="9">
+        <f>B22*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="C36" s="9">
+        <f>C22*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="D36" s="9">
+        <f>D22*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="E36" s="9">
+        <f>E22*Inputs!$E$41</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Yuno proposal vs fixed fee A, $ a month (negative = Yuno cheaper)</t>
-        </is>
-      </c>
-      <c r="B37" s="11">
-        <f>B29-B33</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>C29-C33</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
-        <f>D29-D33</f>
-        <v/>
-      </c>
-      <c r="E37" s="11">
-        <f>E29-E33</f>
+          <t>Fixed fee B, % of TPV</t>
+        </is>
+      </c>
+      <c r="B37" s="36">
+        <f>B36/B23</f>
+        <v/>
+      </c>
+      <c r="C37" s="36">
+        <f>C36/C23</f>
+        <v/>
+      </c>
+      <c r="D37" s="36">
+        <f>D36/D23</f>
+        <v/>
+      </c>
+      <c r="E37" s="36">
+        <f>E36/E23</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
+          <t>Yuno proposal vs fixed fee A, $ a month (negative = Yuno cheaper)</t>
+        </is>
+      </c>
+      <c r="B38" s="9">
+        <f>B30-B34</f>
+        <v/>
+      </c>
+      <c r="C38" s="9">
+        <f>C30-C34</f>
+        <v/>
+      </c>
+      <c r="D38" s="9">
+        <f>D30-D34</f>
+        <v/>
+      </c>
+      <c r="E38" s="9">
+        <f>E30-E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
           <t>Yuno proposal vs fixed fee B, $ a month (negative = Yuno cheaper)</t>
         </is>
       </c>
-      <c r="B38" s="9">
-        <f>B29-B35</f>
-        <v/>
-      </c>
-      <c r="C38" s="9">
-        <f>C29-C35</f>
-        <v/>
-      </c>
-      <c r="D38" s="9">
-        <f>D29-D35</f>
-        <v/>
-      </c>
-      <c r="E38" s="9">
-        <f>E29-E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="B39" s="11">
+        <f>B30-B36</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>C30-C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>D30-D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>E30-E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Small-ticket view at the MEDIAN ticket ($5): same transactions, half the TPV</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B41" s="7">
+      <c r="B42" s="7">
         <f>Inputs!$E$8</f>
         <v/>
       </c>
-      <c r="C41" s="7">
+      <c r="C42" s="7">
         <f>Inputs!$E$9</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D42" s="7">
         <f>Inputs!$E$10</f>
         <v/>
       </c>
-      <c r="E41" s="7">
-        <f>Inputs!$E$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Successful transactions a month</t>
-        </is>
-      </c>
-      <c r="B42" s="50">
-        <f>Inputs!$E$8</f>
-        <v/>
-      </c>
-      <c r="C42" s="50">
-        <f>Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="D42" s="50">
-        <f>Inputs!$E$10</f>
-        <v/>
-      </c>
-      <c r="E42" s="50">
+      <c r="E42" s="7">
         <f>Inputs!$E$11</f>
         <v/>
       </c>
@@ -3045,408 +3145,431 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>TPV a month</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
-        <f>B42*Inputs!$E$7</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>C42*Inputs!$E$7</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>D42*Inputs!$E$7</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>E42*Inputs!$E$7</f>
+          <t>Successful transactions a month</t>
+        </is>
+      </c>
+      <c r="B43" s="30">
+        <f>Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C43" s="30">
+        <f>Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D43" s="30">
+        <f>Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E43" s="30">
+        <f>Inputs!$E$11</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>TPV inside the included block</t>
+          <t>Net TPV a month</t>
         </is>
       </c>
       <c r="B44" s="9">
-        <f>MIN(B42,Inputs!$E$34)*B43/B42</f>
+        <f>B43*Inputs!$E$7</f>
         <v/>
       </c>
       <c r="C44" s="9">
-        <f>MIN(C42,Inputs!$E$34)*C43/C42</f>
+        <f>C43*Inputs!$E$7</f>
         <v/>
       </c>
       <c r="D44" s="9">
-        <f>MIN(D42,Inputs!$E$34)*D43/D42</f>
+        <f>D43*Inputs!$E$7</f>
         <v/>
       </c>
       <c r="E44" s="9">
-        <f>MIN(E42,Inputs!$E$34)*E43/E42</f>
+        <f>E43*Inputs!$E$7</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 1</t>
+          <t>Net TPV inside the included block</t>
         </is>
       </c>
       <c r="B45" s="11">
-        <f>MAX(0,MIN(B43,Inputs!$E$35)-MAX(0,B44))</f>
+        <f>MIN(B44,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="C45" s="11">
-        <f>MAX(0,MIN(C43,Inputs!$E$35)-MAX(0,C44))</f>
+        <f>MIN(C44,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D45" s="11">
-        <f>MAX(0,MIN(D43,Inputs!$E$35)-MAX(0,D44))</f>
+        <f>MIN(D44,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="E45" s="11">
-        <f>MAX(0,MIN(E43,Inputs!$E$35)-MAX(0,E44))</f>
+        <f>MIN(E44,Inputs!$E$34)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 2</t>
+          <t>Billable Net TPV · tranche 1</t>
         </is>
       </c>
       <c r="B46" s="9">
-        <f>MAX(0,MIN(B43,Inputs!$E$37)-MAX(Inputs!$E$35,B44))</f>
+        <f>MAX(0,MIN(B44,Inputs!$E$35)-MAX(0,B45))</f>
         <v/>
       </c>
       <c r="C46" s="9">
-        <f>MAX(0,MIN(C43,Inputs!$E$37)-MAX(Inputs!$E$35,C44))</f>
+        <f>MAX(0,MIN(C44,Inputs!$E$35)-MAX(0,C45))</f>
         <v/>
       </c>
       <c r="D46" s="9">
-        <f>MAX(0,MIN(D43,Inputs!$E$37)-MAX(Inputs!$E$35,D44))</f>
+        <f>MAX(0,MIN(D44,Inputs!$E$35)-MAX(0,D45))</f>
         <v/>
       </c>
       <c r="E46" s="9">
-        <f>MAX(0,MIN(E43,Inputs!$E$37)-MAX(Inputs!$E$35,E44))</f>
+        <f>MAX(0,MIN(E44,Inputs!$E$35)-MAX(0,E45))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Billable TPV · tranche 3</t>
+          <t>Billable Net TPV · tranche 2</t>
         </is>
       </c>
       <c r="B47" s="11">
-        <f>MAX(0,B43-MAX(Inputs!$E$37,B44))</f>
+        <f>MAX(0,MIN(B44,Inputs!$E$37)-MAX(Inputs!$E$35,B45))</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>MAX(0,C43-MAX(Inputs!$E$37,C44))</f>
+        <f>MAX(0,MIN(C44,Inputs!$E$37)-MAX(Inputs!$E$35,C45))</f>
         <v/>
       </c>
       <c r="D47" s="11">
-        <f>MAX(0,D43-MAX(Inputs!$E$37,D44))</f>
+        <f>MAX(0,MIN(D44,Inputs!$E$37)-MAX(Inputs!$E$35,D45))</f>
         <v/>
       </c>
       <c r="E47" s="11">
-        <f>MAX(0,E43-MAX(Inputs!$E$37,E44))</f>
+        <f>MAX(0,MIN(E44,Inputs!$E$37)-MAX(Inputs!$E$35,E45))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Usage fee</t>
+          <t>Billable Net TPV · tranche 3</t>
         </is>
       </c>
       <c r="B48" s="9">
-        <f>B45*Inputs!$E$36+B46*Inputs!$E$38+B47*Inputs!$E$39</f>
+        <f>MAX(0,B44-MAX(Inputs!$E$37,B45))</f>
         <v/>
       </c>
       <c r="C48" s="9">
-        <f>C45*Inputs!$E$36+C46*Inputs!$E$38+C47*Inputs!$E$39</f>
+        <f>MAX(0,C44-MAX(Inputs!$E$37,C45))</f>
         <v/>
       </c>
       <c r="D48" s="9">
-        <f>D45*Inputs!$E$36+D46*Inputs!$E$38+D47*Inputs!$E$39</f>
+        <f>MAX(0,D44-MAX(Inputs!$E$37,D45))</f>
         <v/>
       </c>
       <c r="E48" s="9">
-        <f>E45*Inputs!$E$36+E46*Inputs!$E$38+E47*Inputs!$E$39</f>
+        <f>MAX(0,E44-MAX(Inputs!$E$37,E45))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
+          <t>Usage fee</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>B46*Inputs!$E$36+B47*Inputs!$E$38+B48*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>C46*Inputs!$E$36+C47*Inputs!$E$38+C48*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>D46*Inputs!$E$36+D47*Inputs!$E$38+D48*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="E49" s="11">
+        <f>E46*Inputs!$E$36+E47*Inputs!$E$38+E48*Inputs!$E$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
           <t>Platform fee</t>
         </is>
       </c>
-      <c r="B49" s="11">
+      <c r="B50" s="9">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="C49" s="11">
+      <c r="C50" s="9">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="D49" s="11">
+      <c r="D50" s="9">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
-      <c r="E49" s="11">
+      <c r="E50" s="9">
         <f>Inputs!$E$33</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Yuno total a month</t>
         </is>
       </c>
-      <c r="B50" s="18">
-        <f>B48+B49</f>
-        <v/>
-      </c>
-      <c r="C50" s="18">
-        <f>C48+C49</f>
-        <v/>
-      </c>
-      <c r="D50" s="18">
-        <f>D48+D49</f>
-        <v/>
-      </c>
-      <c r="E50" s="18">
-        <f>E48+E49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="B51" s="16">
+        <f>B49+B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="16">
+        <f>C49+C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="16">
+        <f>D49+D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="16">
+        <f>E49+E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Yuno total a year</t>
         </is>
       </c>
-      <c r="B51" s="11">
-        <f>B50*12</f>
-        <v/>
-      </c>
-      <c r="C51" s="11">
-        <f>C50*12</f>
-        <v/>
-      </c>
-      <c r="D51" s="11">
-        <f>D50*12</f>
-        <v/>
-      </c>
-      <c r="E51" s="11">
-        <f>E50*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Yuno cost, % of TPV</t>
-        </is>
-      </c>
-      <c r="B52" s="51">
-        <f>B50/B43</f>
-        <v/>
-      </c>
-      <c r="C52" s="51">
-        <f>C50/C43</f>
-        <v/>
-      </c>
-      <c r="D52" s="51">
-        <f>D50/D43</f>
-        <v/>
-      </c>
-      <c r="E52" s="51">
-        <f>E50/E43</f>
+      <c r="B52" s="9">
+        <f>B51*12</f>
+        <v/>
+      </c>
+      <c r="C52" s="9">
+        <f>C51*12</f>
+        <v/>
+      </c>
+      <c r="D52" s="9">
+        <f>D51*12</f>
+        <v/>
+      </c>
+      <c r="E52" s="9">
+        <f>E51*12</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
+          <t>Yuno cost, % of TPV</t>
+        </is>
+      </c>
+      <c r="B53" s="51">
+        <f>B51/B44</f>
+        <v/>
+      </c>
+      <c r="C53" s="51">
+        <f>C51/C44</f>
+        <v/>
+      </c>
+      <c r="D53" s="51">
+        <f>D51/D44</f>
+        <v/>
+      </c>
+      <c r="E53" s="51">
+        <f>E51/E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
           <t>Yuno cost per successful transaction</t>
         </is>
       </c>
-      <c r="B53" s="52">
-        <f>B50/B42</f>
-        <v/>
-      </c>
-      <c r="C53" s="52">
-        <f>C50/C42</f>
-        <v/>
-      </c>
-      <c r="D53" s="52">
-        <f>D50/D42</f>
-        <v/>
-      </c>
-      <c r="E53" s="52">
-        <f>E50/E42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Hypothetical fixed fee A a month (comparison)</t>
-        </is>
-      </c>
-      <c r="B54" s="9">
-        <f>B42*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="C54" s="9">
-        <f>C42*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="D54" s="9">
-        <f>D42*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="E54" s="9">
-        <f>E42*Inputs!$E$40</f>
+      <c r="B54" s="52">
+        <f>B51/B43</f>
+        <v/>
+      </c>
+      <c r="C54" s="52">
+        <f>C51/C43</f>
+        <v/>
+      </c>
+      <c r="D54" s="52">
+        <f>D51/D43</f>
+        <v/>
+      </c>
+      <c r="E54" s="52">
+        <f>E51/E43</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fixed fee A, % of TPV</t>
-        </is>
-      </c>
-      <c r="B55" s="36">
-        <f>B54/B43</f>
-        <v/>
-      </c>
-      <c r="C55" s="36">
-        <f>C54/C43</f>
-        <v/>
-      </c>
-      <c r="D55" s="36">
-        <f>D54/D43</f>
-        <v/>
-      </c>
-      <c r="E55" s="36">
-        <f>E54/E43</f>
+          <t>Hypothetical fixed fee A a month (comparison)</t>
+        </is>
+      </c>
+      <c r="B55" s="11">
+        <f>B43*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>C43*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="D55" s="11">
+        <f>D43*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="E55" s="11">
+        <f>E43*Inputs!$E$40</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Hypothetical fixed fee B a month (comparison)</t>
-        </is>
-      </c>
-      <c r="B56" s="9">
-        <f>B42*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="C56" s="9">
-        <f>C42*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="D56" s="9">
-        <f>D42*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="E56" s="9">
-        <f>E42*Inputs!$E$41</f>
+          <t>Fixed fee A, % of TPV</t>
+        </is>
+      </c>
+      <c r="B56" s="12">
+        <f>B55/B44</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>C55/C44</f>
+        <v/>
+      </c>
+      <c r="D56" s="12">
+        <f>D55/D44</f>
+        <v/>
+      </c>
+      <c r="E56" s="12">
+        <f>E55/E44</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Fixed fee B, % of TPV</t>
-        </is>
-      </c>
-      <c r="B57" s="36">
-        <f>B56/B43</f>
-        <v/>
-      </c>
-      <c r="C57" s="36">
-        <f>C56/C43</f>
-        <v/>
-      </c>
-      <c r="D57" s="36">
-        <f>D56/D43</f>
-        <v/>
-      </c>
-      <c r="E57" s="36">
-        <f>E56/E43</f>
+          <t>Hypothetical fixed fee B a month (comparison)</t>
+        </is>
+      </c>
+      <c r="B57" s="11">
+        <f>B43*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>C43*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="D57" s="11">
+        <f>D43*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="E57" s="11">
+        <f>E43*Inputs!$E$41</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Yuno proposal vs fixed fee A, $ a month (negative = Yuno cheaper)</t>
-        </is>
-      </c>
-      <c r="B58" s="9">
-        <f>B50-B54</f>
-        <v/>
-      </c>
-      <c r="C58" s="9">
-        <f>C50-C54</f>
-        <v/>
-      </c>
-      <c r="D58" s="9">
-        <f>D50-D54</f>
-        <v/>
-      </c>
-      <c r="E58" s="9">
-        <f>E50-E54</f>
+          <t>Fixed fee B, % of TPV</t>
+        </is>
+      </c>
+      <c r="B58" s="12">
+        <f>B57/B44</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>C57/C44</f>
+        <v/>
+      </c>
+      <c r="D58" s="12">
+        <f>D57/D44</f>
+        <v/>
+      </c>
+      <c r="E58" s="12">
+        <f>E57/E44</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
+          <t>Yuno proposal vs fixed fee A, $ a month (negative = Yuno cheaper)</t>
+        </is>
+      </c>
+      <c r="B59" s="11">
+        <f>B51-B55</f>
+        <v/>
+      </c>
+      <c r="C59" s="11">
+        <f>C51-C55</f>
+        <v/>
+      </c>
+      <c r="D59" s="11">
+        <f>D51-D55</f>
+        <v/>
+      </c>
+      <c r="E59" s="11">
+        <f>E51-E55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
           <t>Yuno proposal vs fixed fee B, $ a month (negative = Yuno cheaper)</t>
         </is>
       </c>
-      <c r="B59" s="11">
-        <f>B50-B56</f>
-        <v/>
-      </c>
-      <c r="C59" s="11">
-        <f>C50-C56</f>
-        <v/>
-      </c>
-      <c r="D59" s="11">
-        <f>D50-D56</f>
-        <v/>
-      </c>
-      <c r="E59" s="11">
-        <f>E50-E56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="43" t="inlineStr">
-        <is>
-          <t>Reading: a fixed fee per transaction is blind to the ticket. At a $5 median, $0.05 a transaction is 1.0% of TPV and $0.10 is 2.0%. A % of TPV keeps the cost proportional to what Carry1st actually sells.</t>
+      <c r="B60" s="9">
+        <f>B51-B57</f>
+        <v/>
+      </c>
+      <c r="C60" s="9">
+        <f>C51-C57</f>
+        <v/>
+      </c>
+      <c r="D60" s="9">
+        <f>D51-D57</f>
+        <v/>
+      </c>
+      <c r="E60" s="9">
+        <f>E51-E57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>Reading: a fixed fee per transaction is blind to the ticket. At a $5 median, $0.05 a transaction is 1.0% of TPV and $0.10 is 2.0%. Billing in bps on Net TPV keeps the cost proportional to what Carry1st actually sells.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3514,51 +3637,51 @@
           <t>Successful transactions a month</t>
         </is>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="46">
         <f>Inputs!$D$8</f>
         <v/>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="46">
         <f>Inputs!$D$9</f>
         <v/>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="46">
         <f>Inputs!$D$10</f>
         <v/>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="46">
         <f>Inputs!$D$11</f>
         <v/>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="46">
         <f>Inputs!$E$8</f>
         <v/>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="46">
         <f>Inputs!$E$9</f>
         <v/>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="46">
         <f>Inputs!$E$10</f>
         <v/>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="46">
         <f>Inputs!$E$11</f>
         <v/>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="46">
         <f>Inputs!$F$8</f>
         <v/>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="46">
         <f>Inputs!$F$9</f>
         <v/>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="46">
         <f>Inputs!$F$10</f>
         <v/>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="46">
         <f>Inputs!$F$11</f>
         <v/>
       </c>
@@ -3566,7 +3689,7 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>TPV a month (transactions x average ticket)</t>
+          <t>Net TPV a month (transactions x average ticket)</t>
         </is>
       </c>
       <c r="B6" s="18">
@@ -3989,62 +4112,62 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Yuno · TPV inside the included block</t>
+          <t>Yuno · Net TPV inside the included block</t>
         </is>
       </c>
       <c r="B15" s="11">
-        <f>MIN(B5,Inputs!$E$34)*B6/B5</f>
+        <f>MIN(B6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>MIN(C5,Inputs!$E$34)*C6/C5</f>
+        <f>MIN(C6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>MIN(D5,Inputs!$E$34)*D6/D5</f>
+        <f>MIN(D6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>MIN(E5,Inputs!$E$34)*E6/E5</f>
+        <f>MIN(E6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="F15" s="11">
-        <f>MIN(F5,Inputs!$E$34)*F6/F5</f>
+        <f>MIN(F6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="G15" s="11">
-        <f>MIN(G5,Inputs!$E$34)*G6/G5</f>
+        <f>MIN(G6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="H15" s="11">
-        <f>MIN(H5,Inputs!$E$34)*H6/H5</f>
+        <f>MIN(H6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>MIN(I5,Inputs!$E$34)*I6/I5</f>
+        <f>MIN(I6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="J15" s="11">
-        <f>MIN(J5,Inputs!$E$34)*J6/J5</f>
+        <f>MIN(J6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="K15" s="11">
-        <f>MIN(K5,Inputs!$E$34)*K6/K5</f>
+        <f>MIN(K6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="L15" s="11">
-        <f>MIN(L5,Inputs!$E$34)*L6/L5</f>
+        <f>MIN(L6,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="M15" s="11">
-        <f>MIN(M5,Inputs!$E$34)*M6/M5</f>
+        <f>MIN(M6,Inputs!$E$34)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Yuno · billable TPV in tranche 1</t>
+          <t>Yuno · billable Net TPV in tranche 1</t>
         </is>
       </c>
       <c r="B16" s="9">
@@ -4099,7 +4222,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Yuno · billable TPV in tranche 2</t>
+          <t>Yuno · billable Net TPV in tranche 2</t>
         </is>
       </c>
       <c r="B17" s="11">
@@ -4154,7 +4277,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Yuno · billable TPV in tranche 3</t>
+          <t>Yuno · billable Net TPV in tranche 3</t>
         </is>
       </c>
       <c r="B18" s="9">
@@ -5939,7 +6062,7 @@
     <row r="9">
       <c r="A9" s="43" t="inlineStr">
         <is>
-          <t>Break-even = first monthly transaction count at which L1 + L2 + L3 + L4 (contribution view) &gt;= Yuno platform fee + usage. Below the included block, usage is zero, so the test is simply gross benefit &gt;= $7,500.</t>
+          <t>Break-even = first monthly transaction count at which L1 + L2 + L3 + L4 (contribution view) &gt;= Yuno platform fee + usage. Inside the included block, usage is zero, so the test is simply gross benefit &gt;= $7,500.</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6091,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Net TPV</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -6061,7 +6184,7 @@
         <v/>
       </c>
       <c r="C12" s="57">
-        <f>MIN(A12,Inputs!$E$34)*B12/A12</f>
+        <f>MIN(B12,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D12" s="57">
@@ -6135,7 +6258,7 @@
         <v/>
       </c>
       <c r="C13" s="57">
-        <f>MIN(A13,Inputs!$E$34)*B13/A13</f>
+        <f>MIN(B13,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D13" s="57">
@@ -6209,7 +6332,7 @@
         <v/>
       </c>
       <c r="C14" s="57">
-        <f>MIN(A14,Inputs!$E$34)*B14/A14</f>
+        <f>MIN(B14,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D14" s="57">
@@ -6283,7 +6406,7 @@
         <v/>
       </c>
       <c r="C15" s="57">
-        <f>MIN(A15,Inputs!$E$34)*B15/A15</f>
+        <f>MIN(B15,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D15" s="57">
@@ -6357,7 +6480,7 @@
         <v/>
       </c>
       <c r="C16" s="57">
-        <f>MIN(A16,Inputs!$E$34)*B16/A16</f>
+        <f>MIN(B16,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D16" s="57">
@@ -6431,7 +6554,7 @@
         <v/>
       </c>
       <c r="C17" s="57">
-        <f>MIN(A17,Inputs!$E$34)*B17/A17</f>
+        <f>MIN(B17,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D17" s="57">
@@ -6505,7 +6628,7 @@
         <v/>
       </c>
       <c r="C18" s="57">
-        <f>MIN(A18,Inputs!$E$34)*B18/A18</f>
+        <f>MIN(B18,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D18" s="57">
@@ -6579,7 +6702,7 @@
         <v/>
       </c>
       <c r="C19" s="57">
-        <f>MIN(A19,Inputs!$E$34)*B19/A19</f>
+        <f>MIN(B19,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D19" s="57">
@@ -6653,7 +6776,7 @@
         <v/>
       </c>
       <c r="C20" s="57">
-        <f>MIN(A20,Inputs!$E$34)*B20/A20</f>
+        <f>MIN(B20,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D20" s="57">
@@ -6727,7 +6850,7 @@
         <v/>
       </c>
       <c r="C21" s="57">
-        <f>MIN(A21,Inputs!$E$34)*B21/A21</f>
+        <f>MIN(B21,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D21" s="57">
@@ -6801,7 +6924,7 @@
         <v/>
       </c>
       <c r="C22" s="57">
-        <f>MIN(A22,Inputs!$E$34)*B22/A22</f>
+        <f>MIN(B22,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D22" s="57">
@@ -6875,7 +6998,7 @@
         <v/>
       </c>
       <c r="C23" s="57">
-        <f>MIN(A23,Inputs!$E$34)*B23/A23</f>
+        <f>MIN(B23,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D23" s="57">
@@ -6949,7 +7072,7 @@
         <v/>
       </c>
       <c r="C24" s="57">
-        <f>MIN(A24,Inputs!$E$34)*B24/A24</f>
+        <f>MIN(B24,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D24" s="57">
@@ -7023,7 +7146,7 @@
         <v/>
       </c>
       <c r="C25" s="57">
-        <f>MIN(A25,Inputs!$E$34)*B25/A25</f>
+        <f>MIN(B25,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D25" s="57">
@@ -7097,7 +7220,7 @@
         <v/>
       </c>
       <c r="C26" s="57">
-        <f>MIN(A26,Inputs!$E$34)*B26/A26</f>
+        <f>MIN(B26,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D26" s="57">
@@ -7171,7 +7294,7 @@
         <v/>
       </c>
       <c r="C27" s="57">
-        <f>MIN(A27,Inputs!$E$34)*B27/A27</f>
+        <f>MIN(B27,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D27" s="57">
@@ -7245,7 +7368,7 @@
         <v/>
       </c>
       <c r="C28" s="57">
-        <f>MIN(A28,Inputs!$E$34)*B28/A28</f>
+        <f>MIN(B28,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D28" s="57">
@@ -7319,7 +7442,7 @@
         <v/>
       </c>
       <c r="C29" s="57">
-        <f>MIN(A29,Inputs!$E$34)*B29/A29</f>
+        <f>MIN(B29,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D29" s="57">
@@ -7393,7 +7516,7 @@
         <v/>
       </c>
       <c r="C30" s="57">
-        <f>MIN(A30,Inputs!$E$34)*B30/A30</f>
+        <f>MIN(B30,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D30" s="57">
@@ -7467,7 +7590,7 @@
         <v/>
       </c>
       <c r="C31" s="57">
-        <f>MIN(A31,Inputs!$E$34)*B31/A31</f>
+        <f>MIN(B31,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D31" s="57">
@@ -7541,7 +7664,7 @@
         <v/>
       </c>
       <c r="C32" s="57">
-        <f>MIN(A32,Inputs!$E$34)*B32/A32</f>
+        <f>MIN(B32,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D32" s="57">
@@ -7615,7 +7738,7 @@
         <v/>
       </c>
       <c r="C33" s="57">
-        <f>MIN(A33,Inputs!$E$34)*B33/A33</f>
+        <f>MIN(B33,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D33" s="57">
@@ -7689,7 +7812,7 @@
         <v/>
       </c>
       <c r="C34" s="57">
-        <f>MIN(A34,Inputs!$E$34)*B34/A34</f>
+        <f>MIN(B34,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D34" s="57">
@@ -7763,7 +7886,7 @@
         <v/>
       </c>
       <c r="C35" s="57">
-        <f>MIN(A35,Inputs!$E$34)*B35/A35</f>
+        <f>MIN(B35,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D35" s="57">
@@ -7837,7 +7960,7 @@
         <v/>
       </c>
       <c r="C36" s="57">
-        <f>MIN(A36,Inputs!$E$34)*B36/A36</f>
+        <f>MIN(B36,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D36" s="57">
@@ -7911,7 +8034,7 @@
         <v/>
       </c>
       <c r="C37" s="57">
-        <f>MIN(A37,Inputs!$E$34)*B37/A37</f>
+        <f>MIN(B37,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D37" s="57">
@@ -7985,7 +8108,7 @@
         <v/>
       </c>
       <c r="C38" s="57">
-        <f>MIN(A38,Inputs!$E$34)*B38/A38</f>
+        <f>MIN(B38,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D38" s="57">
@@ -8059,7 +8182,7 @@
         <v/>
       </c>
       <c r="C39" s="57">
-        <f>MIN(A39,Inputs!$E$34)*B39/A39</f>
+        <f>MIN(B39,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D39" s="57">
@@ -8133,7 +8256,7 @@
         <v/>
       </c>
       <c r="C40" s="57">
-        <f>MIN(A40,Inputs!$E$34)*B40/A40</f>
+        <f>MIN(B40,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D40" s="57">
@@ -8207,7 +8330,7 @@
         <v/>
       </c>
       <c r="C41" s="57">
-        <f>MIN(A41,Inputs!$E$34)*B41/A41</f>
+        <f>MIN(B41,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D41" s="57">
@@ -8281,7 +8404,7 @@
         <v/>
       </c>
       <c r="C42" s="57">
-        <f>MIN(A42,Inputs!$E$34)*B42/A42</f>
+        <f>MIN(B42,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D42" s="57">
@@ -8355,7 +8478,7 @@
         <v/>
       </c>
       <c r="C43" s="57">
-        <f>MIN(A43,Inputs!$E$34)*B43/A43</f>
+        <f>MIN(B43,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D43" s="57">
@@ -8429,7 +8552,7 @@
         <v/>
       </c>
       <c r="C44" s="57">
-        <f>MIN(A44,Inputs!$E$34)*B44/A44</f>
+        <f>MIN(B44,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D44" s="57">
@@ -8503,7 +8626,7 @@
         <v/>
       </c>
       <c r="C45" s="57">
-        <f>MIN(A45,Inputs!$E$34)*B45/A45</f>
+        <f>MIN(B45,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D45" s="57">
@@ -8577,7 +8700,7 @@
         <v/>
       </c>
       <c r="C46" s="57">
-        <f>MIN(A46,Inputs!$E$34)*B46/A46</f>
+        <f>MIN(B46,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D46" s="57">
@@ -8651,7 +8774,7 @@
         <v/>
       </c>
       <c r="C47" s="57">
-        <f>MIN(A47,Inputs!$E$34)*B47/A47</f>
+        <f>MIN(B47,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D47" s="57">
@@ -8725,7 +8848,7 @@
         <v/>
       </c>
       <c r="C48" s="57">
-        <f>MIN(A48,Inputs!$E$34)*B48/A48</f>
+        <f>MIN(B48,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D48" s="57">
@@ -8799,7 +8922,7 @@
         <v/>
       </c>
       <c r="C49" s="57">
-        <f>MIN(A49,Inputs!$E$34)*B49/A49</f>
+        <f>MIN(B49,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D49" s="57">
@@ -8873,7 +8996,7 @@
         <v/>
       </c>
       <c r="C50" s="57">
-        <f>MIN(A50,Inputs!$E$34)*B50/A50</f>
+        <f>MIN(B50,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D50" s="57">
@@ -8947,7 +9070,7 @@
         <v/>
       </c>
       <c r="C51" s="57">
-        <f>MIN(A51,Inputs!$E$34)*B51/A51</f>
+        <f>MIN(B51,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D51" s="57">
@@ -9021,7 +9144,7 @@
         <v/>
       </c>
       <c r="C52" s="57">
-        <f>MIN(A52,Inputs!$E$34)*B52/A52</f>
+        <f>MIN(B52,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D52" s="57">
@@ -9095,7 +9218,7 @@
         <v/>
       </c>
       <c r="C53" s="57">
-        <f>MIN(A53,Inputs!$E$34)*B53/A53</f>
+        <f>MIN(B53,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D53" s="57">
@@ -9169,7 +9292,7 @@
         <v/>
       </c>
       <c r="C54" s="57">
-        <f>MIN(A54,Inputs!$E$34)*B54/A54</f>
+        <f>MIN(B54,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D54" s="57">
@@ -9243,7 +9366,7 @@
         <v/>
       </c>
       <c r="C55" s="57">
-        <f>MIN(A55,Inputs!$E$34)*B55/A55</f>
+        <f>MIN(B55,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D55" s="57">
@@ -9317,7 +9440,7 @@
         <v/>
       </c>
       <c r="C56" s="57">
-        <f>MIN(A56,Inputs!$E$34)*B56/A56</f>
+        <f>MIN(B56,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D56" s="57">
@@ -9391,7 +9514,7 @@
         <v/>
       </c>
       <c r="C57" s="57">
-        <f>MIN(A57,Inputs!$E$34)*B57/A57</f>
+        <f>MIN(B57,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D57" s="57">
@@ -9465,7 +9588,7 @@
         <v/>
       </c>
       <c r="C58" s="57">
-        <f>MIN(A58,Inputs!$E$34)*B58/A58</f>
+        <f>MIN(B58,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D58" s="57">
@@ -9539,7 +9662,7 @@
         <v/>
       </c>
       <c r="C59" s="57">
-        <f>MIN(A59,Inputs!$E$34)*B59/A59</f>
+        <f>MIN(B59,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D59" s="57">
@@ -9613,7 +9736,7 @@
         <v/>
       </c>
       <c r="C60" s="57">
-        <f>MIN(A60,Inputs!$E$34)*B60/A60</f>
+        <f>MIN(B60,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D60" s="57">
@@ -9687,7 +9810,7 @@
         <v/>
       </c>
       <c r="C61" s="57">
-        <f>MIN(A61,Inputs!$E$34)*B61/A61</f>
+        <f>MIN(B61,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D61" s="57">
@@ -9761,7 +9884,7 @@
         <v/>
       </c>
       <c r="C62" s="57">
-        <f>MIN(A62,Inputs!$E$34)*B62/A62</f>
+        <f>MIN(B62,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D62" s="57">
@@ -9835,7 +9958,7 @@
         <v/>
       </c>
       <c r="C63" s="57">
-        <f>MIN(A63,Inputs!$E$34)*B63/A63</f>
+        <f>MIN(B63,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D63" s="57">
@@ -9909,7 +10032,7 @@
         <v/>
       </c>
       <c r="C64" s="57">
-        <f>MIN(A64,Inputs!$E$34)*B64/A64</f>
+        <f>MIN(B64,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D64" s="57">
@@ -9983,7 +10106,7 @@
         <v/>
       </c>
       <c r="C65" s="57">
-        <f>MIN(A65,Inputs!$E$34)*B65/A65</f>
+        <f>MIN(B65,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D65" s="57">
@@ -10057,7 +10180,7 @@
         <v/>
       </c>
       <c r="C66" s="57">
-        <f>MIN(A66,Inputs!$E$34)*B66/A66</f>
+        <f>MIN(B66,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D66" s="57">
@@ -10131,7 +10254,7 @@
         <v/>
       </c>
       <c r="C67" s="57">
-        <f>MIN(A67,Inputs!$E$34)*B67/A67</f>
+        <f>MIN(B67,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D67" s="57">
@@ -10205,7 +10328,7 @@
         <v/>
       </c>
       <c r="C68" s="57">
-        <f>MIN(A68,Inputs!$E$34)*B68/A68</f>
+        <f>MIN(B68,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D68" s="57">
@@ -10279,7 +10402,7 @@
         <v/>
       </c>
       <c r="C69" s="57">
-        <f>MIN(A69,Inputs!$E$34)*B69/A69</f>
+        <f>MIN(B69,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D69" s="57">
@@ -10353,7 +10476,7 @@
         <v/>
       </c>
       <c r="C70" s="57">
-        <f>MIN(A70,Inputs!$E$34)*B70/A70</f>
+        <f>MIN(B70,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D70" s="57">
@@ -10427,7 +10550,7 @@
         <v/>
       </c>
       <c r="C71" s="57">
-        <f>MIN(A71,Inputs!$E$34)*B71/A71</f>
+        <f>MIN(B71,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D71" s="57">
@@ -10501,7 +10624,7 @@
         <v/>
       </c>
       <c r="C72" s="57">
-        <f>MIN(A72,Inputs!$E$34)*B72/A72</f>
+        <f>MIN(B72,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D72" s="57">
@@ -10575,7 +10698,7 @@
         <v/>
       </c>
       <c r="C73" s="57">
-        <f>MIN(A73,Inputs!$E$34)*B73/A73</f>
+        <f>MIN(B73,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D73" s="57">
@@ -10649,7 +10772,7 @@
         <v/>
       </c>
       <c r="C74" s="57">
-        <f>MIN(A74,Inputs!$E$34)*B74/A74</f>
+        <f>MIN(B74,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D74" s="57">
@@ -10723,7 +10846,7 @@
         <v/>
       </c>
       <c r="C75" s="57">
-        <f>MIN(A75,Inputs!$E$34)*B75/A75</f>
+        <f>MIN(B75,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D75" s="57">
@@ -10797,7 +10920,7 @@
         <v/>
       </c>
       <c r="C76" s="57">
-        <f>MIN(A76,Inputs!$E$34)*B76/A76</f>
+        <f>MIN(B76,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D76" s="57">
@@ -10871,7 +10994,7 @@
         <v/>
       </c>
       <c r="C77" s="57">
-        <f>MIN(A77,Inputs!$E$34)*B77/A77</f>
+        <f>MIN(B77,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D77" s="57">
@@ -10945,7 +11068,7 @@
         <v/>
       </c>
       <c r="C78" s="57">
-        <f>MIN(A78,Inputs!$E$34)*B78/A78</f>
+        <f>MIN(B78,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D78" s="57">
@@ -11019,7 +11142,7 @@
         <v/>
       </c>
       <c r="C79" s="57">
-        <f>MIN(A79,Inputs!$E$34)*B79/A79</f>
+        <f>MIN(B79,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D79" s="57">
@@ -11093,7 +11216,7 @@
         <v/>
       </c>
       <c r="C80" s="57">
-        <f>MIN(A80,Inputs!$E$34)*B80/A80</f>
+        <f>MIN(B80,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D80" s="57">
@@ -11167,7 +11290,7 @@
         <v/>
       </c>
       <c r="C81" s="57">
-        <f>MIN(A81,Inputs!$E$34)*B81/A81</f>
+        <f>MIN(B81,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D81" s="57">
@@ -11241,7 +11364,7 @@
         <v/>
       </c>
       <c r="C82" s="57">
-        <f>MIN(A82,Inputs!$E$34)*B82/A82</f>
+        <f>MIN(B82,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D82" s="57">
@@ -11315,7 +11438,7 @@
         <v/>
       </c>
       <c r="C83" s="57">
-        <f>MIN(A83,Inputs!$E$34)*B83/A83</f>
+        <f>MIN(B83,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D83" s="57">
@@ -11389,7 +11512,7 @@
         <v/>
       </c>
       <c r="C84" s="57">
-        <f>MIN(A84,Inputs!$E$34)*B84/A84</f>
+        <f>MIN(B84,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D84" s="57">
@@ -11463,7 +11586,7 @@
         <v/>
       </c>
       <c r="C85" s="57">
-        <f>MIN(A85,Inputs!$E$34)*B85/A85</f>
+        <f>MIN(B85,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D85" s="57">
@@ -11537,7 +11660,7 @@
         <v/>
       </c>
       <c r="C86" s="57">
-        <f>MIN(A86,Inputs!$E$34)*B86/A86</f>
+        <f>MIN(B86,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D86" s="57">
@@ -11611,7 +11734,7 @@
         <v/>
       </c>
       <c r="C87" s="57">
-        <f>MIN(A87,Inputs!$E$34)*B87/A87</f>
+        <f>MIN(B87,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D87" s="57">
@@ -11685,7 +11808,7 @@
         <v/>
       </c>
       <c r="C88" s="57">
-        <f>MIN(A88,Inputs!$E$34)*B88/A88</f>
+        <f>MIN(B88,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D88" s="57">
@@ -11759,7 +11882,7 @@
         <v/>
       </c>
       <c r="C89" s="57">
-        <f>MIN(A89,Inputs!$E$34)*B89/A89</f>
+        <f>MIN(B89,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D89" s="57">
@@ -11833,7 +11956,7 @@
         <v/>
       </c>
       <c r="C90" s="57">
-        <f>MIN(A90,Inputs!$E$34)*B90/A90</f>
+        <f>MIN(B90,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D90" s="57">
@@ -11907,7 +12030,7 @@
         <v/>
       </c>
       <c r="C91" s="57">
-        <f>MIN(A91,Inputs!$E$34)*B91/A91</f>
+        <f>MIN(B91,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D91" s="57">
@@ -11981,7 +12104,7 @@
         <v/>
       </c>
       <c r="C92" s="57">
-        <f>MIN(A92,Inputs!$E$34)*B92/A92</f>
+        <f>MIN(B92,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D92" s="57">
@@ -12055,7 +12178,7 @@
         <v/>
       </c>
       <c r="C93" s="57">
-        <f>MIN(A93,Inputs!$E$34)*B93/A93</f>
+        <f>MIN(B93,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D93" s="57">
@@ -12129,7 +12252,7 @@
         <v/>
       </c>
       <c r="C94" s="57">
-        <f>MIN(A94,Inputs!$E$34)*B94/A94</f>
+        <f>MIN(B94,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D94" s="57">
@@ -12203,7 +12326,7 @@
         <v/>
       </c>
       <c r="C95" s="57">
-        <f>MIN(A95,Inputs!$E$34)*B95/A95</f>
+        <f>MIN(B95,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D95" s="57">
@@ -12277,7 +12400,7 @@
         <v/>
       </c>
       <c r="C96" s="57">
-        <f>MIN(A96,Inputs!$E$34)*B96/A96</f>
+        <f>MIN(B96,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D96" s="57">
@@ -12351,7 +12474,7 @@
         <v/>
       </c>
       <c r="C97" s="57">
-        <f>MIN(A97,Inputs!$E$34)*B97/A97</f>
+        <f>MIN(B97,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D97" s="57">
@@ -12425,7 +12548,7 @@
         <v/>
       </c>
       <c r="C98" s="57">
-        <f>MIN(A98,Inputs!$E$34)*B98/A98</f>
+        <f>MIN(B98,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D98" s="57">
@@ -12499,7 +12622,7 @@
         <v/>
       </c>
       <c r="C99" s="57">
-        <f>MIN(A99,Inputs!$E$34)*B99/A99</f>
+        <f>MIN(B99,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D99" s="57">
@@ -12573,7 +12696,7 @@
         <v/>
       </c>
       <c r="C100" s="57">
-        <f>MIN(A100,Inputs!$E$34)*B100/A100</f>
+        <f>MIN(B100,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D100" s="57">
@@ -12647,7 +12770,7 @@
         <v/>
       </c>
       <c r="C101" s="57">
-        <f>MIN(A101,Inputs!$E$34)*B101/A101</f>
+        <f>MIN(B101,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D101" s="57">
@@ -12721,7 +12844,7 @@
         <v/>
       </c>
       <c r="C102" s="57">
-        <f>MIN(A102,Inputs!$E$34)*B102/A102</f>
+        <f>MIN(B102,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D102" s="57">
@@ -12795,7 +12918,7 @@
         <v/>
       </c>
       <c r="C103" s="57">
-        <f>MIN(A103,Inputs!$E$34)*B103/A103</f>
+        <f>MIN(B103,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D103" s="57">
@@ -12869,7 +12992,7 @@
         <v/>
       </c>
       <c r="C104" s="57">
-        <f>MIN(A104,Inputs!$E$34)*B104/A104</f>
+        <f>MIN(B104,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D104" s="57">
@@ -12943,7 +13066,7 @@
         <v/>
       </c>
       <c r="C105" s="57">
-        <f>MIN(A105,Inputs!$E$34)*B105/A105</f>
+        <f>MIN(B105,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D105" s="57">
@@ -13017,7 +13140,7 @@
         <v/>
       </c>
       <c r="C106" s="57">
-        <f>MIN(A106,Inputs!$E$34)*B106/A106</f>
+        <f>MIN(B106,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D106" s="57">
@@ -13091,7 +13214,7 @@
         <v/>
       </c>
       <c r="C107" s="57">
-        <f>MIN(A107,Inputs!$E$34)*B107/A107</f>
+        <f>MIN(B107,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D107" s="57">
@@ -13165,7 +13288,7 @@
         <v/>
       </c>
       <c r="C108" s="57">
-        <f>MIN(A108,Inputs!$E$34)*B108/A108</f>
+        <f>MIN(B108,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D108" s="57">
@@ -13239,7 +13362,7 @@
         <v/>
       </c>
       <c r="C109" s="57">
-        <f>MIN(A109,Inputs!$E$34)*B109/A109</f>
+        <f>MIN(B109,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D109" s="57">
@@ -13313,7 +13436,7 @@
         <v/>
       </c>
       <c r="C110" s="57">
-        <f>MIN(A110,Inputs!$E$34)*B110/A110</f>
+        <f>MIN(B110,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D110" s="57">
@@ -13387,7 +13510,7 @@
         <v/>
       </c>
       <c r="C111" s="57">
-        <f>MIN(A111,Inputs!$E$34)*B111/A111</f>
+        <f>MIN(B111,Inputs!$E$34)</f>
         <v/>
       </c>
       <c r="D111" s="57">
@@ -13474,12 +13597,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -13496,6 +13619,7 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -13508,7 +13632,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Payback month = first month in which the cumulative net benefit (contribution view) is non-negative. No upfront fee: the only cost is the monthly Yuno bill.</t>
+          <t>Payback month = first month in which the cumulative net benefit (contribution view) is non-negative. The INTERNAL launch credit switch (Inputs section 9) applies on this sheet only; default off.</t>
         </is>
       </c>
     </row>
@@ -13547,15 +13671,15 @@
         </is>
       </c>
       <c r="C5" s="62">
-        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,H12:H24,0)),"not within the ramp")</f>
+        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,I12:I24,0)),"not within the ramp")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>G24</f>
+        <f>H24</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>D25</f>
+        <f>E25</f>
         <v/>
       </c>
       <c r="I5" s="44">
@@ -13570,15 +13694,15 @@
         </is>
       </c>
       <c r="C6" s="62">
-        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,M12:M24,0)),"not within the ramp")</f>
+        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,N12:N24,0)),"not within the ramp")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>L24</f>
+        <f>M24</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>I25</f>
+        <f>J25</f>
         <v/>
       </c>
       <c r="I6" s="44">
@@ -13593,15 +13717,15 @@
         </is>
       </c>
       <c r="C7" s="62">
-        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,R12:R24,0)),"not within the ramp")</f>
+        <f>IFERROR(INDEX($A$12:$A$24,MATCH(1,S12:S24,0)),"not within the ramp")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>Q24</f>
+        <f>R24</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>N25</f>
+        <f>O25</f>
         <v/>
       </c>
       <c r="I7" s="44">
@@ -13617,17 +13741,17 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -13646,80 +13770,85 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>Net TPV</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
+          <t>Credit (if on)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
           <t>Yuno cost</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Gross contribution</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Net benefit</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Cumulative net</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Cum &gt;= 0</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Yuno cost</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>Gross contribution</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>Net benefit</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Cumulative net</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Cum &gt;= 0</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Yuno cost</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Gross contribution</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Net benefit</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Cumulative net</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Cum &gt;= 0</t>
         </is>
@@ -13740,63 +13869,67 @@
         <v/>
       </c>
       <c r="D12" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,1&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E12" s="57">
-        <f>C12*Inputs!$D$20/10000+(C12/Inputs!$D$22*Inputs!$D$23+C12*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C12*(Inputs!$D$16-Inputs!$D$20/10000)+D12)/C12))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F12" s="59">
-        <f>E12-D12</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(C12,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C12,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(C12,Inputs!$E$34))))*Inputs!$E$39-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="57">
+        <f>C12*Inputs!$D$20/10000+(C12/Inputs!$D$22*Inputs!$D$23+C12*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C12*(Inputs!$D$16-Inputs!$D$20/10000)+E12)/C12))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G12" s="59">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="60">
-        <f>IF(G12&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$39</f>
+        <f>F12-E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="60">
+        <f>IF(H12&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J12" s="57">
-        <f>C12*Inputs!$E$20/10000+(C12/Inputs!$E$22*Inputs!$E$23+C12*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C12*(Inputs!$E$16-Inputs!$E$20/10000)+I12)/C12))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K12" s="59">
-        <f>J12-I12</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(C12,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C12,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(C12,Inputs!$E$34))))*Inputs!$E$39-D12</f>
+        <v/>
+      </c>
+      <c r="K12" s="57">
+        <f>C12*Inputs!$E$20/10000+(C12/Inputs!$E$22*Inputs!$E$23+C12*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C12*(Inputs!$E$16-Inputs!$E$20/10000)+J12)/C12))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L12" s="59">
-        <f>K12</f>
-        <v/>
-      </c>
-      <c r="M12" s="60">
-        <f>IF(L12&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N12" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(B12,Inputs!$E$34)*C12/B12)))*Inputs!$E$39</f>
+        <f>K12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="59">
+        <f>L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="60">
+        <f>IF(M12&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O12" s="57">
-        <f>C12*Inputs!$F$20/10000+(C12/Inputs!$F$22*Inputs!$F$23+C12*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C12*(Inputs!$F$16-Inputs!$F$20/10000)+N12)/C12))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P12" s="59">
-        <f>O12-N12</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C12,Inputs!$E$35)-MAX(0,(MIN(C12,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C12,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C12,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C12-MAX(Inputs!$E$37,(MIN(C12,Inputs!$E$34))))*Inputs!$E$39-D12</f>
+        <v/>
+      </c>
+      <c r="P12" s="57">
+        <f>C12*Inputs!$F$20/10000+(C12/Inputs!$F$22*Inputs!$F$23+C12*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C12*(Inputs!$F$16-Inputs!$F$20/10000)+O12)/C12))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q12" s="59">
-        <f>P12</f>
-        <v/>
-      </c>
-      <c r="R12" s="60">
-        <f>IF(Q12&gt;=0,1,0)</f>
+        <f>P12-O12</f>
+        <v/>
+      </c>
+      <c r="R12" s="59">
+        <f>Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="60">
+        <f>IF(R12&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -13815,63 +13948,67 @@
         <v/>
       </c>
       <c r="D13" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,2&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E13" s="57">
-        <f>C13*Inputs!$D$20/10000+(C13/Inputs!$D$22*Inputs!$D$23+C13*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C13*(Inputs!$D$16-Inputs!$D$20/10000)+D13)/C13))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F13" s="59">
-        <f>E13-D13</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(C13,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C13,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(C13,Inputs!$E$34))))*Inputs!$E$39-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="57">
+        <f>C13*Inputs!$D$20/10000+(C13/Inputs!$D$22*Inputs!$D$23+C13*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C13*(Inputs!$D$16-Inputs!$D$20/10000)+E13)/C13))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G13" s="59">
-        <f>G12+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="60">
-        <f>IF(G13&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$39</f>
+        <f>F13-E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="59">
+        <f>H12+G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="60">
+        <f>IF(H13&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J13" s="57">
-        <f>C13*Inputs!$E$20/10000+(C13/Inputs!$E$22*Inputs!$E$23+C13*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C13*(Inputs!$E$16-Inputs!$E$20/10000)+I13)/C13))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K13" s="59">
-        <f>J13-I13</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(C13,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C13,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(C13,Inputs!$E$34))))*Inputs!$E$39-D13</f>
+        <v/>
+      </c>
+      <c r="K13" s="57">
+        <f>C13*Inputs!$E$20/10000+(C13/Inputs!$E$22*Inputs!$E$23+C13*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C13*(Inputs!$E$16-Inputs!$E$20/10000)+J13)/C13))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L13" s="59">
-        <f>L12+K13</f>
-        <v/>
-      </c>
-      <c r="M13" s="60">
-        <f>IF(L13&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N13" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(B13,Inputs!$E$34)*C13/B13)))*Inputs!$E$39</f>
+        <f>K13-J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="59">
+        <f>M12+L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="60">
+        <f>IF(M13&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O13" s="57">
-        <f>C13*Inputs!$F$20/10000+(C13/Inputs!$F$22*Inputs!$F$23+C13*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C13*(Inputs!$F$16-Inputs!$F$20/10000)+N13)/C13))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P13" s="59">
-        <f>O13-N13</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C13,Inputs!$E$35)-MAX(0,(MIN(C13,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C13,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C13,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C13-MAX(Inputs!$E$37,(MIN(C13,Inputs!$E$34))))*Inputs!$E$39-D13</f>
+        <v/>
+      </c>
+      <c r="P13" s="57">
+        <f>C13*Inputs!$F$20/10000+(C13/Inputs!$F$22*Inputs!$F$23+C13*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C13*(Inputs!$F$16-Inputs!$F$20/10000)+O13)/C13))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q13" s="59">
-        <f>Q12+P13</f>
-        <v/>
-      </c>
-      <c r="R13" s="60">
-        <f>IF(Q13&gt;=0,1,0)</f>
+        <f>P13-O13</f>
+        <v/>
+      </c>
+      <c r="R13" s="59">
+        <f>R12+Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="60">
+        <f>IF(R13&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -13890,63 +14027,67 @@
         <v/>
       </c>
       <c r="D14" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,3&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E14" s="57">
-        <f>C14*Inputs!$D$20/10000+(C14/Inputs!$D$22*Inputs!$D$23+C14*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C14*(Inputs!$D$16-Inputs!$D$20/10000)+D14)/C14))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F14" s="59">
-        <f>E14-D14</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(C14,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C14,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(C14,Inputs!$E$34))))*Inputs!$E$39-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="57">
+        <f>C14*Inputs!$D$20/10000+(C14/Inputs!$D$22*Inputs!$D$23+C14*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C14*(Inputs!$D$16-Inputs!$D$20/10000)+E14)/C14))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G14" s="59">
-        <f>G13+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="60">
-        <f>IF(G14&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$39</f>
+        <f>F14-E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="59">
+        <f>H13+G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="60">
+        <f>IF(H14&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J14" s="57">
-        <f>C14*Inputs!$E$20/10000+(C14/Inputs!$E$22*Inputs!$E$23+C14*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C14*(Inputs!$E$16-Inputs!$E$20/10000)+I14)/C14))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K14" s="59">
-        <f>J14-I14</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(C14,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C14,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(C14,Inputs!$E$34))))*Inputs!$E$39-D14</f>
+        <v/>
+      </c>
+      <c r="K14" s="57">
+        <f>C14*Inputs!$E$20/10000+(C14/Inputs!$E$22*Inputs!$E$23+C14*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C14*(Inputs!$E$16-Inputs!$E$20/10000)+J14)/C14))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L14" s="59">
-        <f>L13+K14</f>
-        <v/>
-      </c>
-      <c r="M14" s="60">
-        <f>IF(L14&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N14" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(B14,Inputs!$E$34)*C14/B14)))*Inputs!$E$39</f>
+        <f>K14-J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="59">
+        <f>M13+L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="60">
+        <f>IF(M14&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O14" s="57">
-        <f>C14*Inputs!$F$20/10000+(C14/Inputs!$F$22*Inputs!$F$23+C14*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C14*(Inputs!$F$16-Inputs!$F$20/10000)+N14)/C14))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P14" s="59">
-        <f>O14-N14</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C14,Inputs!$E$35)-MAX(0,(MIN(C14,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C14,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C14,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C14-MAX(Inputs!$E$37,(MIN(C14,Inputs!$E$34))))*Inputs!$E$39-D14</f>
+        <v/>
+      </c>
+      <c r="P14" s="57">
+        <f>C14*Inputs!$F$20/10000+(C14/Inputs!$F$22*Inputs!$F$23+C14*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C14*(Inputs!$F$16-Inputs!$F$20/10000)+O14)/C14))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q14" s="59">
-        <f>Q13+P14</f>
-        <v/>
-      </c>
-      <c r="R14" s="60">
-        <f>IF(Q14&gt;=0,1,0)</f>
+        <f>P14-O14</f>
+        <v/>
+      </c>
+      <c r="R14" s="59">
+        <f>R13+Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="60">
+        <f>IF(R14&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -13965,63 +14106,67 @@
         <v/>
       </c>
       <c r="D15" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,4&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E15" s="57">
-        <f>C15*Inputs!$D$20/10000+(C15/Inputs!$D$22*Inputs!$D$23+C15*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C15*(Inputs!$D$16-Inputs!$D$20/10000)+D15)/C15))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F15" s="59">
-        <f>E15-D15</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(C15,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C15,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(C15,Inputs!$E$34))))*Inputs!$E$39-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="57">
+        <f>C15*Inputs!$D$20/10000+(C15/Inputs!$D$22*Inputs!$D$23+C15*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C15*(Inputs!$D$16-Inputs!$D$20/10000)+E15)/C15))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G15" s="59">
-        <f>G14+F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="60">
-        <f>IF(G15&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$39</f>
+        <f>F15-E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>H14+G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="60">
+        <f>IF(H15&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J15" s="57">
-        <f>C15*Inputs!$E$20/10000+(C15/Inputs!$E$22*Inputs!$E$23+C15*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C15*(Inputs!$E$16-Inputs!$E$20/10000)+I15)/C15))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K15" s="59">
-        <f>J15-I15</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(C15,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C15,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(C15,Inputs!$E$34))))*Inputs!$E$39-D15</f>
+        <v/>
+      </c>
+      <c r="K15" s="57">
+        <f>C15*Inputs!$E$20/10000+(C15/Inputs!$E$22*Inputs!$E$23+C15*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C15*(Inputs!$E$16-Inputs!$E$20/10000)+J15)/C15))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L15" s="59">
-        <f>L14+K15</f>
-        <v/>
-      </c>
-      <c r="M15" s="60">
-        <f>IF(L15&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N15" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(B15,Inputs!$E$34)*C15/B15)))*Inputs!$E$39</f>
+        <f>K15-J15</f>
+        <v/>
+      </c>
+      <c r="M15" s="59">
+        <f>M14+L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="60">
+        <f>IF(M15&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O15" s="57">
-        <f>C15*Inputs!$F$20/10000+(C15/Inputs!$F$22*Inputs!$F$23+C15*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C15*(Inputs!$F$16-Inputs!$F$20/10000)+N15)/C15))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P15" s="59">
-        <f>O15-N15</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C15,Inputs!$E$35)-MAX(0,(MIN(C15,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C15,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C15,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C15-MAX(Inputs!$E$37,(MIN(C15,Inputs!$E$34))))*Inputs!$E$39-D15</f>
+        <v/>
+      </c>
+      <c r="P15" s="57">
+        <f>C15*Inputs!$F$20/10000+(C15/Inputs!$F$22*Inputs!$F$23+C15*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C15*(Inputs!$F$16-Inputs!$F$20/10000)+O15)/C15))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q15" s="59">
-        <f>Q14+P15</f>
-        <v/>
-      </c>
-      <c r="R15" s="60">
-        <f>IF(Q15&gt;=0,1,0)</f>
+        <f>P15-O15</f>
+        <v/>
+      </c>
+      <c r="R15" s="59">
+        <f>R14+Q15</f>
+        <v/>
+      </c>
+      <c r="S15" s="60">
+        <f>IF(R15&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14040,63 +14185,67 @@
         <v/>
       </c>
       <c r="D16" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,5&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E16" s="57">
-        <f>C16*Inputs!$D$20/10000+(C16/Inputs!$D$22*Inputs!$D$23+C16*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C16*(Inputs!$D$16-Inputs!$D$20/10000)+D16)/C16))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F16" s="59">
-        <f>E16-D16</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(C16,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C16,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(C16,Inputs!$E$34))))*Inputs!$E$39-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="57">
+        <f>C16*Inputs!$D$20/10000+(C16/Inputs!$D$22*Inputs!$D$23+C16*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C16*(Inputs!$D$16-Inputs!$D$20/10000)+E16)/C16))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G16" s="59">
-        <f>G15+F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="60">
-        <f>IF(G16&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$39</f>
+        <f>F16-E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="59">
+        <f>H15+G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="60">
+        <f>IF(H16&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J16" s="57">
-        <f>C16*Inputs!$E$20/10000+(C16/Inputs!$E$22*Inputs!$E$23+C16*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C16*(Inputs!$E$16-Inputs!$E$20/10000)+I16)/C16))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K16" s="59">
-        <f>J16-I16</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(C16,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C16,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(C16,Inputs!$E$34))))*Inputs!$E$39-D16</f>
+        <v/>
+      </c>
+      <c r="K16" s="57">
+        <f>C16*Inputs!$E$20/10000+(C16/Inputs!$E$22*Inputs!$E$23+C16*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C16*(Inputs!$E$16-Inputs!$E$20/10000)+J16)/C16))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L16" s="59">
-        <f>L15+K16</f>
-        <v/>
-      </c>
-      <c r="M16" s="60">
-        <f>IF(L16&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N16" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(B16,Inputs!$E$34)*C16/B16)))*Inputs!$E$39</f>
+        <f>K16-J16</f>
+        <v/>
+      </c>
+      <c r="M16" s="59">
+        <f>M15+L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="60">
+        <f>IF(M16&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O16" s="57">
-        <f>C16*Inputs!$F$20/10000+(C16/Inputs!$F$22*Inputs!$F$23+C16*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C16*(Inputs!$F$16-Inputs!$F$20/10000)+N16)/C16))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P16" s="59">
-        <f>O16-N16</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C16,Inputs!$E$35)-MAX(0,(MIN(C16,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C16,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C16,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C16-MAX(Inputs!$E$37,(MIN(C16,Inputs!$E$34))))*Inputs!$E$39-D16</f>
+        <v/>
+      </c>
+      <c r="P16" s="57">
+        <f>C16*Inputs!$F$20/10000+(C16/Inputs!$F$22*Inputs!$F$23+C16*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C16*(Inputs!$F$16-Inputs!$F$20/10000)+O16)/C16))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q16" s="59">
-        <f>Q15+P16</f>
-        <v/>
-      </c>
-      <c r="R16" s="60">
-        <f>IF(Q16&gt;=0,1,0)</f>
+        <f>P16-O16</f>
+        <v/>
+      </c>
+      <c r="R16" s="59">
+        <f>R15+Q16</f>
+        <v/>
+      </c>
+      <c r="S16" s="60">
+        <f>IF(R16&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14115,63 +14264,67 @@
         <v/>
       </c>
       <c r="D17" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,6&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E17" s="57">
-        <f>C17*Inputs!$D$20/10000+(C17/Inputs!$D$22*Inputs!$D$23+C17*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C17*(Inputs!$D$16-Inputs!$D$20/10000)+D17)/C17))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F17" s="59">
-        <f>E17-D17</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(C17,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C17,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(C17,Inputs!$E$34))))*Inputs!$E$39-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="57">
+        <f>C17*Inputs!$D$20/10000+(C17/Inputs!$D$22*Inputs!$D$23+C17*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C17*(Inputs!$D$16-Inputs!$D$20/10000)+E17)/C17))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G17" s="59">
-        <f>G16+F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="60">
-        <f>IF(G17&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$39</f>
+        <f>F17-E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="59">
+        <f>H16+G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="60">
+        <f>IF(H17&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J17" s="57">
-        <f>C17*Inputs!$E$20/10000+(C17/Inputs!$E$22*Inputs!$E$23+C17*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C17*(Inputs!$E$16-Inputs!$E$20/10000)+I17)/C17))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K17" s="59">
-        <f>J17-I17</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(C17,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C17,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(C17,Inputs!$E$34))))*Inputs!$E$39-D17</f>
+        <v/>
+      </c>
+      <c r="K17" s="57">
+        <f>C17*Inputs!$E$20/10000+(C17/Inputs!$E$22*Inputs!$E$23+C17*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C17*(Inputs!$E$16-Inputs!$E$20/10000)+J17)/C17))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L17" s="59">
-        <f>L16+K17</f>
-        <v/>
-      </c>
-      <c r="M17" s="60">
-        <f>IF(L17&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N17" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(B17,Inputs!$E$34)*C17/B17)))*Inputs!$E$39</f>
+        <f>K17-J17</f>
+        <v/>
+      </c>
+      <c r="M17" s="59">
+        <f>M16+L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="60">
+        <f>IF(M17&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O17" s="57">
-        <f>C17*Inputs!$F$20/10000+(C17/Inputs!$F$22*Inputs!$F$23+C17*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C17*(Inputs!$F$16-Inputs!$F$20/10000)+N17)/C17))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P17" s="59">
-        <f>O17-N17</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(C17,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C17,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(C17,Inputs!$E$34))))*Inputs!$E$39-D17</f>
+        <v/>
+      </c>
+      <c r="P17" s="57">
+        <f>C17*Inputs!$F$20/10000+(C17/Inputs!$F$22*Inputs!$F$23+C17*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C17*(Inputs!$F$16-Inputs!$F$20/10000)+O17)/C17))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q17" s="59">
-        <f>Q16+P17</f>
-        <v/>
-      </c>
-      <c r="R17" s="60">
-        <f>IF(Q17&gt;=0,1,0)</f>
+        <f>P17-O17</f>
+        <v/>
+      </c>
+      <c r="R17" s="59">
+        <f>R16+Q17</f>
+        <v/>
+      </c>
+      <c r="S17" s="60">
+        <f>IF(R17&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14190,63 +14343,67 @@
         <v/>
       </c>
       <c r="D18" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,7&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E18" s="57">
-        <f>C18*Inputs!$D$20/10000+(C18/Inputs!$D$22*Inputs!$D$23+C18*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C18*(Inputs!$D$16-Inputs!$D$20/10000)+D18)/C18))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F18" s="59">
-        <f>E18-D18</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(C18,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C18,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(C18,Inputs!$E$34))))*Inputs!$E$39-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="57">
+        <f>C18*Inputs!$D$20/10000+(C18/Inputs!$D$22*Inputs!$D$23+C18*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C18*(Inputs!$D$16-Inputs!$D$20/10000)+E18)/C18))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G18" s="59">
-        <f>G17+F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="60">
-        <f>IF(G18&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$39</f>
+        <f>F18-E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="59">
+        <f>H17+G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="60">
+        <f>IF(H18&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J18" s="57">
-        <f>C18*Inputs!$E$20/10000+(C18/Inputs!$E$22*Inputs!$E$23+C18*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C18*(Inputs!$E$16-Inputs!$E$20/10000)+I18)/C18))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K18" s="59">
-        <f>J18-I18</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(C18,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C18,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(C18,Inputs!$E$34))))*Inputs!$E$39-D18</f>
+        <v/>
+      </c>
+      <c r="K18" s="57">
+        <f>C18*Inputs!$E$20/10000+(C18/Inputs!$E$22*Inputs!$E$23+C18*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C18*(Inputs!$E$16-Inputs!$E$20/10000)+J18)/C18))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L18" s="59">
-        <f>L17+K18</f>
-        <v/>
-      </c>
-      <c r="M18" s="60">
-        <f>IF(L18&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N18" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(B18,Inputs!$E$34)*C18/B18)))*Inputs!$E$39</f>
+        <f>K18-J18</f>
+        <v/>
+      </c>
+      <c r="M18" s="59">
+        <f>M17+L18</f>
+        <v/>
+      </c>
+      <c r="N18" s="60">
+        <f>IF(M18&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O18" s="57">
-        <f>C18*Inputs!$F$20/10000+(C18/Inputs!$F$22*Inputs!$F$23+C18*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C18*(Inputs!$F$16-Inputs!$F$20/10000)+N18)/C18))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P18" s="59">
-        <f>O18-N18</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C18,Inputs!$E$35)-MAX(0,(MIN(C18,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C18,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C18,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C18-MAX(Inputs!$E$37,(MIN(C18,Inputs!$E$34))))*Inputs!$E$39-D18</f>
+        <v/>
+      </c>
+      <c r="P18" s="57">
+        <f>C18*Inputs!$F$20/10000+(C18/Inputs!$F$22*Inputs!$F$23+C18*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C18*(Inputs!$F$16-Inputs!$F$20/10000)+O18)/C18))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q18" s="59">
-        <f>Q17+P18</f>
-        <v/>
-      </c>
-      <c r="R18" s="60">
-        <f>IF(Q18&gt;=0,1,0)</f>
+        <f>P18-O18</f>
+        <v/>
+      </c>
+      <c r="R18" s="59">
+        <f>R17+Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="60">
+        <f>IF(R18&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14265,63 +14422,67 @@
         <v/>
       </c>
       <c r="D19" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,8&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E19" s="57">
-        <f>C19*Inputs!$D$20/10000+(C19/Inputs!$D$22*Inputs!$D$23+C19*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C19*(Inputs!$D$16-Inputs!$D$20/10000)+D19)/C19))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F19" s="59">
-        <f>E19-D19</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(C19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(C19,Inputs!$E$34))))*Inputs!$E$39-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="57">
+        <f>C19*Inputs!$D$20/10000+(C19/Inputs!$D$22*Inputs!$D$23+C19*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C19*(Inputs!$D$16-Inputs!$D$20/10000)+E19)/C19))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G19" s="59">
-        <f>G18+F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="60">
-        <f>IF(G19&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$39</f>
+        <f>F19-E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>H18+G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="60">
+        <f>IF(H19&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J19" s="57">
-        <f>C19*Inputs!$E$20/10000+(C19/Inputs!$E$22*Inputs!$E$23+C19*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C19*(Inputs!$E$16-Inputs!$E$20/10000)+I19)/C19))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K19" s="59">
-        <f>J19-I19</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(C19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(C19,Inputs!$E$34))))*Inputs!$E$39-D19</f>
+        <v/>
+      </c>
+      <c r="K19" s="57">
+        <f>C19*Inputs!$E$20/10000+(C19/Inputs!$E$22*Inputs!$E$23+C19*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C19*(Inputs!$E$16-Inputs!$E$20/10000)+J19)/C19))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L19" s="59">
-        <f>L18+K19</f>
-        <v/>
-      </c>
-      <c r="M19" s="60">
-        <f>IF(L19&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N19" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(B19,Inputs!$E$34)*C19/B19)))*Inputs!$E$39</f>
+        <f>K19-J19</f>
+        <v/>
+      </c>
+      <c r="M19" s="59">
+        <f>M18+L19</f>
+        <v/>
+      </c>
+      <c r="N19" s="60">
+        <f>IF(M19&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O19" s="57">
-        <f>C19*Inputs!$F$20/10000+(C19/Inputs!$F$22*Inputs!$F$23+C19*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C19*(Inputs!$F$16-Inputs!$F$20/10000)+N19)/C19))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P19" s="59">
-        <f>O19-N19</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(C19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(C19,Inputs!$E$34))))*Inputs!$E$39-D19</f>
+        <v/>
+      </c>
+      <c r="P19" s="57">
+        <f>C19*Inputs!$F$20/10000+(C19/Inputs!$F$22*Inputs!$F$23+C19*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C19*(Inputs!$F$16-Inputs!$F$20/10000)+O19)/C19))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q19" s="59">
-        <f>Q18+P19</f>
-        <v/>
-      </c>
-      <c r="R19" s="60">
-        <f>IF(Q19&gt;=0,1,0)</f>
+        <f>P19-O19</f>
+        <v/>
+      </c>
+      <c r="R19" s="59">
+        <f>R18+Q19</f>
+        <v/>
+      </c>
+      <c r="S19" s="60">
+        <f>IF(R19&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14340,63 +14501,67 @@
         <v/>
       </c>
       <c r="D20" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,9&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E20" s="57">
-        <f>C20*Inputs!$D$20/10000+(C20/Inputs!$D$22*Inputs!$D$23+C20*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C20*(Inputs!$D$16-Inputs!$D$20/10000)+D20)/C20))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F20" s="59">
-        <f>E20-D20</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(C20,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C20,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(C20,Inputs!$E$34))))*Inputs!$E$39-D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="57">
+        <f>C20*Inputs!$D$20/10000+(C20/Inputs!$D$22*Inputs!$D$23+C20*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C20*(Inputs!$D$16-Inputs!$D$20/10000)+E20)/C20))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G20" s="59">
-        <f>G19+F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="60">
-        <f>IF(G20&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$39</f>
+        <f>F20-E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>H19+G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="60">
+        <f>IF(H20&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J20" s="57">
-        <f>C20*Inputs!$E$20/10000+(C20/Inputs!$E$22*Inputs!$E$23+C20*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C20*(Inputs!$E$16-Inputs!$E$20/10000)+I20)/C20))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K20" s="59">
-        <f>J20-I20</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(C20,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C20,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(C20,Inputs!$E$34))))*Inputs!$E$39-D20</f>
+        <v/>
+      </c>
+      <c r="K20" s="57">
+        <f>C20*Inputs!$E$20/10000+(C20/Inputs!$E$22*Inputs!$E$23+C20*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C20*(Inputs!$E$16-Inputs!$E$20/10000)+J20)/C20))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L20" s="59">
-        <f>L19+K20</f>
-        <v/>
-      </c>
-      <c r="M20" s="60">
-        <f>IF(L20&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N20" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(B20,Inputs!$E$34)*C20/B20)))*Inputs!$E$39</f>
+        <f>K20-J20</f>
+        <v/>
+      </c>
+      <c r="M20" s="59">
+        <f>M19+L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="60">
+        <f>IF(M20&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O20" s="57">
-        <f>C20*Inputs!$F$20/10000+(C20/Inputs!$F$22*Inputs!$F$23+C20*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C20*(Inputs!$F$16-Inputs!$F$20/10000)+N20)/C20))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P20" s="59">
-        <f>O20-N20</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C20,Inputs!$E$35)-MAX(0,(MIN(C20,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C20,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C20,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C20-MAX(Inputs!$E$37,(MIN(C20,Inputs!$E$34))))*Inputs!$E$39-D20</f>
+        <v/>
+      </c>
+      <c r="P20" s="57">
+        <f>C20*Inputs!$F$20/10000+(C20/Inputs!$F$22*Inputs!$F$23+C20*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C20*(Inputs!$F$16-Inputs!$F$20/10000)+O20)/C20))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q20" s="59">
-        <f>Q19+P20</f>
-        <v/>
-      </c>
-      <c r="R20" s="60">
-        <f>IF(Q20&gt;=0,1,0)</f>
+        <f>P20-O20</f>
+        <v/>
+      </c>
+      <c r="R20" s="59">
+        <f>R19+Q20</f>
+        <v/>
+      </c>
+      <c r="S20" s="60">
+        <f>IF(R20&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14415,63 +14580,67 @@
         <v/>
       </c>
       <c r="D21" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,10&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E21" s="57">
-        <f>C21*Inputs!$D$20/10000+(C21/Inputs!$D$22*Inputs!$D$23+C21*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C21*(Inputs!$D$16-Inputs!$D$20/10000)+D21)/C21))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F21" s="59">
-        <f>E21-D21</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(C21,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C21,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(C21,Inputs!$E$34))))*Inputs!$E$39-D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="57">
+        <f>C21*Inputs!$D$20/10000+(C21/Inputs!$D$22*Inputs!$D$23+C21*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C21*(Inputs!$D$16-Inputs!$D$20/10000)+E21)/C21))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G21" s="59">
-        <f>G20+F21</f>
-        <v/>
-      </c>
-      <c r="H21" s="60">
-        <f>IF(G21&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$39</f>
+        <f>F21-E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="59">
+        <f>H20+G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="60">
+        <f>IF(H21&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J21" s="57">
-        <f>C21*Inputs!$E$20/10000+(C21/Inputs!$E$22*Inputs!$E$23+C21*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C21*(Inputs!$E$16-Inputs!$E$20/10000)+I21)/C21))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K21" s="59">
-        <f>J21-I21</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(C21,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C21,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(C21,Inputs!$E$34))))*Inputs!$E$39-D21</f>
+        <v/>
+      </c>
+      <c r="K21" s="57">
+        <f>C21*Inputs!$E$20/10000+(C21/Inputs!$E$22*Inputs!$E$23+C21*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C21*(Inputs!$E$16-Inputs!$E$20/10000)+J21)/C21))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L21" s="59">
-        <f>L20+K21</f>
-        <v/>
-      </c>
-      <c r="M21" s="60">
-        <f>IF(L21&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(B21,Inputs!$E$34)*C21/B21)))*Inputs!$E$39</f>
+        <f>K21-J21</f>
+        <v/>
+      </c>
+      <c r="M21" s="59">
+        <f>M20+L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="60">
+        <f>IF(M21&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O21" s="57">
-        <f>C21*Inputs!$F$20/10000+(C21/Inputs!$F$22*Inputs!$F$23+C21*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C21*(Inputs!$F$16-Inputs!$F$20/10000)+N21)/C21))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P21" s="59">
-        <f>O21-N21</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C21,Inputs!$E$35)-MAX(0,(MIN(C21,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C21,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C21,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C21-MAX(Inputs!$E$37,(MIN(C21,Inputs!$E$34))))*Inputs!$E$39-D21</f>
+        <v/>
+      </c>
+      <c r="P21" s="57">
+        <f>C21*Inputs!$F$20/10000+(C21/Inputs!$F$22*Inputs!$F$23+C21*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C21*(Inputs!$F$16-Inputs!$F$20/10000)+O21)/C21))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q21" s="59">
-        <f>Q20+P21</f>
-        <v/>
-      </c>
-      <c r="R21" s="60">
-        <f>IF(Q21&gt;=0,1,0)</f>
+        <f>P21-O21</f>
+        <v/>
+      </c>
+      <c r="R21" s="59">
+        <f>R20+Q21</f>
+        <v/>
+      </c>
+      <c r="S21" s="60">
+        <f>IF(R21&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14490,63 +14659,67 @@
         <v/>
       </c>
       <c r="D22" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,11&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E22" s="57">
-        <f>C22*Inputs!$D$20/10000+(C22/Inputs!$D$22*Inputs!$D$23+C22*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C22*(Inputs!$D$16-Inputs!$D$20/10000)+D22)/C22))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F22" s="59">
-        <f>E22-D22</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(C22,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C22,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(C22,Inputs!$E$34))))*Inputs!$E$39-D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="57">
+        <f>C22*Inputs!$D$20/10000+(C22/Inputs!$D$22*Inputs!$D$23+C22*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C22*(Inputs!$D$16-Inputs!$D$20/10000)+E22)/C22))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G22" s="59">
-        <f>G21+F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="60">
-        <f>IF(G22&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$39</f>
+        <f>F22-E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="59">
+        <f>H21+G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="60">
+        <f>IF(H22&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J22" s="57">
-        <f>C22*Inputs!$E$20/10000+(C22/Inputs!$E$22*Inputs!$E$23+C22*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C22*(Inputs!$E$16-Inputs!$E$20/10000)+I22)/C22))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K22" s="59">
-        <f>J22-I22</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(C22,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C22,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(C22,Inputs!$E$34))))*Inputs!$E$39-D22</f>
+        <v/>
+      </c>
+      <c r="K22" s="57">
+        <f>C22*Inputs!$E$20/10000+(C22/Inputs!$E$22*Inputs!$E$23+C22*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C22*(Inputs!$E$16-Inputs!$E$20/10000)+J22)/C22))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L22" s="59">
-        <f>L21+K22</f>
-        <v/>
-      </c>
-      <c r="M22" s="60">
-        <f>IF(L22&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(B22,Inputs!$E$34)*C22/B22)))*Inputs!$E$39</f>
+        <f>K22-J22</f>
+        <v/>
+      </c>
+      <c r="M22" s="59">
+        <f>M21+L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="60">
+        <f>IF(M22&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O22" s="57">
-        <f>C22*Inputs!$F$20/10000+(C22/Inputs!$F$22*Inputs!$F$23+C22*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C22*(Inputs!$F$16-Inputs!$F$20/10000)+N22)/C22))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P22" s="59">
-        <f>O22-N22</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C22,Inputs!$E$35)-MAX(0,(MIN(C22,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C22,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C22,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C22-MAX(Inputs!$E$37,(MIN(C22,Inputs!$E$34))))*Inputs!$E$39-D22</f>
+        <v/>
+      </c>
+      <c r="P22" s="57">
+        <f>C22*Inputs!$F$20/10000+(C22/Inputs!$F$22*Inputs!$F$23+C22*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C22*(Inputs!$F$16-Inputs!$F$20/10000)+O22)/C22))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q22" s="59">
-        <f>Q21+P22</f>
-        <v/>
-      </c>
-      <c r="R22" s="60">
-        <f>IF(Q22&gt;=0,1,0)</f>
+        <f>P22-O22</f>
+        <v/>
+      </c>
+      <c r="R22" s="59">
+        <f>R21+Q22</f>
+        <v/>
+      </c>
+      <c r="S22" s="60">
+        <f>IF(R22&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14565,63 +14738,67 @@
         <v/>
       </c>
       <c r="D23" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,12&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E23" s="57">
-        <f>C23*Inputs!$D$20/10000+(C23/Inputs!$D$22*Inputs!$D$23+C23*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C23*(Inputs!$D$16-Inputs!$D$20/10000)+D23)/C23))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F23" s="59">
-        <f>E23-D23</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(C23,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C23,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(C23,Inputs!$E$34))))*Inputs!$E$39-D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="57">
+        <f>C23*Inputs!$D$20/10000+(C23/Inputs!$D$22*Inputs!$D$23+C23*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C23*(Inputs!$D$16-Inputs!$D$20/10000)+E23)/C23))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G23" s="59">
-        <f>G22+F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="60">
-        <f>IF(G23&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$39</f>
+        <f>F23-E23</f>
+        <v/>
+      </c>
+      <c r="H23" s="59">
+        <f>H22+G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="60">
+        <f>IF(H23&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J23" s="57">
-        <f>C23*Inputs!$E$20/10000+(C23/Inputs!$E$22*Inputs!$E$23+C23*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C23*(Inputs!$E$16-Inputs!$E$20/10000)+I23)/C23))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K23" s="59">
-        <f>J23-I23</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(C23,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C23,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(C23,Inputs!$E$34))))*Inputs!$E$39-D23</f>
+        <v/>
+      </c>
+      <c r="K23" s="57">
+        <f>C23*Inputs!$E$20/10000+(C23/Inputs!$E$22*Inputs!$E$23+C23*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C23*(Inputs!$E$16-Inputs!$E$20/10000)+J23)/C23))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L23" s="59">
-        <f>L22+K23</f>
-        <v/>
-      </c>
-      <c r="M23" s="60">
-        <f>IF(L23&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(B23,Inputs!$E$34)*C23/B23)))*Inputs!$E$39</f>
+        <f>K23-J23</f>
+        <v/>
+      </c>
+      <c r="M23" s="59">
+        <f>M22+L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="60">
+        <f>IF(M23&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O23" s="57">
-        <f>C23*Inputs!$F$20/10000+(C23/Inputs!$F$22*Inputs!$F$23+C23*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C23*(Inputs!$F$16-Inputs!$F$20/10000)+N23)/C23))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P23" s="59">
-        <f>O23-N23</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C23,Inputs!$E$35)-MAX(0,(MIN(C23,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C23,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C23,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C23-MAX(Inputs!$E$37,(MIN(C23,Inputs!$E$34))))*Inputs!$E$39-D23</f>
+        <v/>
+      </c>
+      <c r="P23" s="57">
+        <f>C23*Inputs!$F$20/10000+(C23/Inputs!$F$22*Inputs!$F$23+C23*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C23*(Inputs!$F$16-Inputs!$F$20/10000)+O23)/C23))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q23" s="59">
-        <f>Q22+P23</f>
-        <v/>
-      </c>
-      <c r="R23" s="60">
-        <f>IF(Q23&gt;=0,1,0)</f>
+        <f>P23-O23</f>
+        <v/>
+      </c>
+      <c r="R23" s="59">
+        <f>R22+Q23</f>
+        <v/>
+      </c>
+      <c r="S23" s="60">
+        <f>IF(R23&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14640,63 +14817,67 @@
         <v/>
       </c>
       <c r="D24" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$39</f>
+        <f>IF(AND(Inputs!$E$45=1,13&lt;=Inputs!$E$47),Inputs!$E$46,0)</f>
         <v/>
       </c>
       <c r="E24" s="57">
-        <f>C24*Inputs!$D$20/10000+(C24/Inputs!$D$22*Inputs!$D$23+C24*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C24*(Inputs!$D$16-Inputs!$D$20/10000)+D24)/C24))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
-        <v/>
-      </c>
-      <c r="F24" s="59">
-        <f>E24-D24</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(C24,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C24,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(C24,Inputs!$E$34))))*Inputs!$E$39-D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="57">
+        <f>C24*Inputs!$D$20/10000+(C24/Inputs!$D$22*Inputs!$D$23+C24*Inputs!$D$25)*(Inputs!$D$13-Inputs!$D$14*((C24*(Inputs!$D$16-Inputs!$D$20/10000)+E24)/C24))+Inputs!$D$27*Inputs!$D$28*Inputs!$D$29*(1+Inputs!$D$30*Inputs!$D$31/12)/Inputs!$D$31</f>
         <v/>
       </c>
       <c r="G24" s="59">
-        <f>G23+F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="60">
-        <f>IF(G24&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$39</f>
+        <f>F24-E24</f>
+        <v/>
+      </c>
+      <c r="H24" s="59">
+        <f>H23+G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="60">
+        <f>IF(H24&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="J24" s="57">
-        <f>C24*Inputs!$E$20/10000+(C24/Inputs!$E$22*Inputs!$E$23+C24*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C24*(Inputs!$E$16-Inputs!$E$20/10000)+I24)/C24))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
-        <v/>
-      </c>
-      <c r="K24" s="59">
-        <f>J24-I24</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(C24,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C24,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(C24,Inputs!$E$34))))*Inputs!$E$39-D24</f>
+        <v/>
+      </c>
+      <c r="K24" s="57">
+        <f>C24*Inputs!$E$20/10000+(C24/Inputs!$E$22*Inputs!$E$23+C24*Inputs!$E$25)*(Inputs!$E$13-Inputs!$E$14*((C24*(Inputs!$E$16-Inputs!$E$20/10000)+J24)/C24))+Inputs!$E$27*Inputs!$E$28*Inputs!$E$29*(1+Inputs!$E$30*Inputs!$E$31/12)/Inputs!$E$31</f>
         <v/>
       </c>
       <c r="L24" s="59">
-        <f>L23+K24</f>
-        <v/>
-      </c>
-      <c r="M24" s="60">
-        <f>IF(L24&gt;=0,1,0)</f>
-        <v/>
-      </c>
-      <c r="N24" s="57">
-        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(B24,Inputs!$E$34)*C24/B24)))*Inputs!$E$39</f>
+        <f>K24-J24</f>
+        <v/>
+      </c>
+      <c r="M24" s="59">
+        <f>M23+L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="60">
+        <f>IF(M24&gt;=0,1,0)</f>
         <v/>
       </c>
       <c r="O24" s="57">
-        <f>C24*Inputs!$F$20/10000+(C24/Inputs!$F$22*Inputs!$F$23+C24*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C24*(Inputs!$F$16-Inputs!$F$20/10000)+N24)/C24))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
-        <v/>
-      </c>
-      <c r="P24" s="59">
-        <f>O24-N24</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C24,Inputs!$E$35)-MAX(0,(MIN(C24,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C24,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C24,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C24-MAX(Inputs!$E$37,(MIN(C24,Inputs!$E$34))))*Inputs!$E$39-D24</f>
+        <v/>
+      </c>
+      <c r="P24" s="57">
+        <f>C24*Inputs!$F$20/10000+(C24/Inputs!$F$22*Inputs!$F$23+C24*Inputs!$F$25)*(Inputs!$F$13-Inputs!$F$14*((C24*(Inputs!$F$16-Inputs!$F$20/10000)+O24)/C24))+Inputs!$F$27*Inputs!$F$28*Inputs!$F$29*(1+Inputs!$F$30*Inputs!$F$31/12)/Inputs!$F$31</f>
         <v/>
       </c>
       <c r="Q24" s="59">
-        <f>Q23+P24</f>
-        <v/>
-      </c>
-      <c r="R24" s="60">
-        <f>IF(Q24&gt;=0,1,0)</f>
+        <f>P24-O24</f>
+        <v/>
+      </c>
+      <c r="R24" s="59">
+        <f>R23+Q24</f>
+        <v/>
+      </c>
+      <c r="S24" s="60">
+        <f>IF(R24&gt;=0,1,0)</f>
         <v/>
       </c>
     </row>
@@ -14726,8 +14907,8 @@
         <f>SUM(F12:F24)</f>
         <v/>
       </c>
-      <c r="I25" s="65">
-        <f>SUM(I12:I24)</f>
+      <c r="G25" s="65">
+        <f>SUM(G12:G24)</f>
         <v/>
       </c>
       <c r="J25" s="65">
@@ -14738,8 +14919,8 @@
         <f>SUM(K12:K24)</f>
         <v/>
       </c>
-      <c r="N25" s="65">
-        <f>SUM(N12:N24)</f>
+      <c r="L25" s="65">
+        <f>SUM(L12:L24)</f>
         <v/>
       </c>
       <c r="O25" s="65">
@@ -14750,18 +14931,22 @@
         <f>SUM(P12:P24)</f>
         <v/>
       </c>
+      <c r="Q25" s="65">
+        <f>SUM(Q12:Q24)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="N10:R10"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="A2:T2"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14774,7 +14959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -14851,7 +15036,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   TPV a month</t>
+          <t xml:space="preserve">   Net TPV a month</t>
         </is>
       </c>
       <c r="B7" s="11">
@@ -14878,141 +15063,141 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(B7,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$8,Inputs!$E$34)*B7/Inputs!$E$8)))*Inputs!$E$36+MAX(0,MIN(B7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$8,Inputs!$E$34)*B7/Inputs!$E$8)))*Inputs!$E$38+MAX(0,B7-MAX(Inputs!$E$37,(MIN(Inputs!$E$8,Inputs!$E$34)*B7/Inputs!$E$8)))*Inputs!$E$39</f>
+        <f>Inputs!$E$33+MAX(0,MIN(B7,Inputs!$E$35)-MAX(0,(MIN(B7,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(B7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B7,Inputs!$E$34))))*Inputs!$E$38+MAX(0,B7-MAX(Inputs!$E$37,(MIN(B7,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(C7,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$9,Inputs!$E$34)*C7/Inputs!$E$9)))*Inputs!$E$36+MAX(0,MIN(C7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$9,Inputs!$E$34)*C7/Inputs!$E$9)))*Inputs!$E$38+MAX(0,C7-MAX(Inputs!$E$37,(MIN(Inputs!$E$9,Inputs!$E$34)*C7/Inputs!$E$9)))*Inputs!$E$39</f>
+        <f>Inputs!$E$33+MAX(0,MIN(C7,Inputs!$E$35)-MAX(0,(MIN(C7,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C7,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C7-MAX(Inputs!$E$37,(MIN(C7,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(D7,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$10,Inputs!$E$34)*D7/Inputs!$E$10)))*Inputs!$E$36+MAX(0,MIN(D7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$10,Inputs!$E$34)*D7/Inputs!$E$10)))*Inputs!$E$38+MAX(0,D7-MAX(Inputs!$E$37,(MIN(Inputs!$E$10,Inputs!$E$34)*D7/Inputs!$E$10)))*Inputs!$E$39</f>
+        <f>Inputs!$E$33+MAX(0,MIN(D7,Inputs!$E$35)-MAX(0,(MIN(D7,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(D7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(D7,Inputs!$E$34))))*Inputs!$E$38+MAX(0,D7-MAX(Inputs!$E$37,(MIN(D7,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(E7,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$11,Inputs!$E$34)*E7/Inputs!$E$11)))*Inputs!$E$36+MAX(0,MIN(E7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$11,Inputs!$E$34)*E7/Inputs!$E$11)))*Inputs!$E$38+MAX(0,E7-MAX(Inputs!$E$37,(MIN(Inputs!$E$11,Inputs!$E$34)*E7/Inputs!$E$11)))*Inputs!$E$39</f>
+        <f>Inputs!$E$33+MAX(0,MIN(E7,Inputs!$E$35)-MAX(0,(MIN(E7,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(E7,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(E7,Inputs!$E$34))))*Inputs!$E$38+MAX(0,E7-MAX(Inputs!$E$37,(MIN(E7,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yuno, % of TPV</t>
-        </is>
-      </c>
-      <c r="B9" s="48">
-        <f>B8/B7</f>
-        <v/>
-      </c>
-      <c r="C9" s="48">
-        <f>C8/C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="48">
-        <f>D8/D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="48">
-        <f>E8/E7</f>
+          <t xml:space="preserve">   Yuno usage only</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B8-Inputs!$E$33</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C8-Inputs!$E$33</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D8-Inputs!$E$33</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>E8-Inputs!$E$33</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yuno, $ per transaction</t>
-        </is>
-      </c>
-      <c r="B10" s="42">
-        <f>B8/Inputs!$E$8</f>
-        <v/>
-      </c>
-      <c r="C10" s="42">
-        <f>C8/Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="D10" s="42">
-        <f>D8/Inputs!$E$10</f>
-        <v/>
-      </c>
-      <c r="E10" s="42">
-        <f>E8/Inputs!$E$11</f>
+          <t xml:space="preserve">   Yuno, % of TPV</t>
+        </is>
+      </c>
+      <c r="B10" s="51">
+        <f>B8/B7</f>
+        <v/>
+      </c>
+      <c r="C10" s="51">
+        <f>C8/C7</f>
+        <v/>
+      </c>
+      <c r="D10" s="51">
+        <f>D8/D7</f>
+        <v/>
+      </c>
+      <c r="E10" s="51">
+        <f>E8/E7</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A a month</t>
-        </is>
-      </c>
-      <c r="B11" s="11">
-        <f>Inputs!$E$8*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="C11" s="11">
-        <f>Inputs!$E$9*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>Inputs!$E$10*Inputs!$E$40</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>Inputs!$E$11*Inputs!$E$40</f>
+          <t xml:space="preserve">   Yuno, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B11" s="42">
+        <f>B8/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C11" s="42">
+        <f>C8/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D11" s="42">
+        <f>D8/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E11" s="42">
+        <f>E8/Inputs!$E$11</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
-        </is>
-      </c>
-      <c r="B12" s="36">
-        <f>B11/B7</f>
-        <v/>
-      </c>
-      <c r="C12" s="36">
-        <f>C11/C7</f>
-        <v/>
-      </c>
-      <c r="D12" s="36">
-        <f>D11/D7</f>
-        <v/>
-      </c>
-      <c r="E12" s="36">
-        <f>E11/E7</f>
+          <t xml:space="preserve">   Yuno usage only, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B12" s="42">
+        <f>B9/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C12" s="42">
+        <f>C9/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D12" s="42">
+        <f>D9/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E12" s="42">
+        <f>E9/Inputs!$E$11</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee B a month</t>
+          <t xml:space="preserve">   Fixed fee A a month</t>
         </is>
       </c>
       <c r="B13" s="11">
-        <f>Inputs!$E$8*Inputs!$E$41</f>
+        <f>Inputs!$E$8*Inputs!$E$40</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>Inputs!$E$9*Inputs!$E$41</f>
+        <f>Inputs!$E$9*Inputs!$E$40</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>Inputs!$E$10*Inputs!$E$41</f>
+        <f>Inputs!$E$10*Inputs!$E$40</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>Inputs!$E$11*Inputs!$E$41</f>
+        <f>Inputs!$E$11*Inputs!$E$40</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee B, % of TPV</t>
+          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
         </is>
       </c>
       <c r="B14" s="36">
@@ -15032,619 +15217,757 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee B a month</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>Inputs!$E$8*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>Inputs!$E$9*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>Inputs!$E$10*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>Inputs!$E$11*Inputs!$E$41</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee B, % of TPV</t>
+        </is>
+      </c>
+      <c r="B16" s="36">
+        <f>B15/B7</f>
+        <v/>
+      </c>
+      <c r="C16" s="36">
+        <f>C15/C7</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>D15/D7</f>
+        <v/>
+      </c>
+      <c r="E16" s="36">
+        <f>E15/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="63" t="inlineStr">
         <is>
           <t>Ticket $10 (average)</t>
         </is>
       </c>
-      <c r="B16" s="66">
+      <c r="B18" s="66">
         <f>Inputs!$E$6</f>
         <v/>
       </c>
-      <c r="C16" s="67" t="n"/>
-      <c r="D16" s="67" t="n"/>
-      <c r="E16" s="67" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   TPV a month</t>
-        </is>
-      </c>
-      <c r="B17" s="11">
-        <f>Inputs!$E$8*$B$16</f>
-        <v/>
-      </c>
-      <c r="C17" s="11">
-        <f>Inputs!$E$9*$B$16</f>
-        <v/>
-      </c>
-      <c r="D17" s="11">
-        <f>Inputs!$E$10*$B$16</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>Inputs!$E$11*$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Yuno total a month</t>
-        </is>
-      </c>
-      <c r="B18" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(B17,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$8,Inputs!$E$34)*B17/Inputs!$E$8)))*Inputs!$E$36+MAX(0,MIN(B17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$8,Inputs!$E$34)*B17/Inputs!$E$8)))*Inputs!$E$38+MAX(0,B17-MAX(Inputs!$E$37,(MIN(Inputs!$E$8,Inputs!$E$34)*B17/Inputs!$E$8)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="C18" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(C17,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$9,Inputs!$E$34)*C17/Inputs!$E$9)))*Inputs!$E$36+MAX(0,MIN(C17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$9,Inputs!$E$34)*C17/Inputs!$E$9)))*Inputs!$E$38+MAX(0,C17-MAX(Inputs!$E$37,(MIN(Inputs!$E$9,Inputs!$E$34)*C17/Inputs!$E$9)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="D18" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(D17,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$10,Inputs!$E$34)*D17/Inputs!$E$10)))*Inputs!$E$36+MAX(0,MIN(D17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$10,Inputs!$E$34)*D17/Inputs!$E$10)))*Inputs!$E$38+MAX(0,D17-MAX(Inputs!$E$37,(MIN(Inputs!$E$10,Inputs!$E$34)*D17/Inputs!$E$10)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(E17,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$11,Inputs!$E$34)*E17/Inputs!$E$11)))*Inputs!$E$36+MAX(0,MIN(E17,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$11,Inputs!$E$34)*E17/Inputs!$E$11)))*Inputs!$E$38+MAX(0,E17-MAX(Inputs!$E$37,(MIN(Inputs!$E$11,Inputs!$E$34)*E17/Inputs!$E$11)))*Inputs!$E$39</f>
-        <v/>
-      </c>
+      <c r="C18" s="67" t="n"/>
+      <c r="D18" s="67" t="n"/>
+      <c r="E18" s="67" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yuno, % of TPV</t>
-        </is>
-      </c>
-      <c r="B19" s="48">
-        <f>B18/B17</f>
-        <v/>
-      </c>
-      <c r="C19" s="48">
-        <f>C18/C17</f>
-        <v/>
-      </c>
-      <c r="D19" s="48">
-        <f>D18/D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="48">
-        <f>E18/E17</f>
+          <t xml:space="preserve">   Net TPV a month</t>
+        </is>
+      </c>
+      <c r="B19" s="11">
+        <f>Inputs!$E$8*$B$18</f>
+        <v/>
+      </c>
+      <c r="C19" s="11">
+        <f>Inputs!$E$9*$B$18</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>Inputs!$E$10*$B$18</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>Inputs!$E$11*$B$18</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yuno, $ per transaction</t>
-        </is>
-      </c>
-      <c r="B20" s="42">
-        <f>B18/Inputs!$E$8</f>
-        <v/>
-      </c>
-      <c r="C20" s="42">
-        <f>C18/Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="D20" s="42">
-        <f>D18/Inputs!$E$10</f>
-        <v/>
-      </c>
-      <c r="E20" s="42">
-        <f>E18/Inputs!$E$11</f>
+          <t xml:space="preserve">   Yuno total a month</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(B19,Inputs!$E$35)-MAX(0,(MIN(B19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(B19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,B19-MAX(Inputs!$E$37,(MIN(B19,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(C19,Inputs!$E$35)-MAX(0,(MIN(C19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C19-MAX(Inputs!$E$37,(MIN(C19,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="D20" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(D19,Inputs!$E$35)-MAX(0,(MIN(D19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(D19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(D19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,D19-MAX(Inputs!$E$37,(MIN(D19,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(E19,Inputs!$E$35)-MAX(0,(MIN(E19,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(E19,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(E19,Inputs!$E$34))))*Inputs!$E$38+MAX(0,E19-MAX(Inputs!$E$37,(MIN(E19,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A a month</t>
+          <t xml:space="preserve">   Yuno usage only</t>
         </is>
       </c>
       <c r="B21" s="11">
-        <f>Inputs!$E$8*Inputs!$E$40</f>
+        <f>B20-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="C21" s="11">
-        <f>Inputs!$E$9*Inputs!$E$40</f>
+        <f>C20-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="D21" s="11">
-        <f>Inputs!$E$10*Inputs!$E$40</f>
+        <f>D20-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="E21" s="11">
-        <f>Inputs!$E$11*Inputs!$E$40</f>
+        <f>E20-Inputs!$E$33</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
-        </is>
-      </c>
-      <c r="B22" s="36">
-        <f>B21/B17</f>
-        <v/>
-      </c>
-      <c r="C22" s="36">
-        <f>C21/C17</f>
-        <v/>
-      </c>
-      <c r="D22" s="36">
-        <f>D21/D17</f>
-        <v/>
-      </c>
-      <c r="E22" s="36">
-        <f>E21/E17</f>
+          <t xml:space="preserve">   Yuno, % of TPV</t>
+        </is>
+      </c>
+      <c r="B22" s="51">
+        <f>B20/B19</f>
+        <v/>
+      </c>
+      <c r="C22" s="51">
+        <f>C20/C19</f>
+        <v/>
+      </c>
+      <c r="D22" s="51">
+        <f>D20/D19</f>
+        <v/>
+      </c>
+      <c r="E22" s="51">
+        <f>E20/E19</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee B a month</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
-        <f>Inputs!$E$8*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="C23" s="11">
-        <f>Inputs!$E$9*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>Inputs!$E$10*Inputs!$E$41</f>
-        <v/>
-      </c>
-      <c r="E23" s="11">
-        <f>Inputs!$E$11*Inputs!$E$41</f>
+          <t xml:space="preserve">   Yuno, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B23" s="42">
+        <f>B20/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C23" s="42">
+        <f>C20/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D23" s="42">
+        <f>D20/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E23" s="42">
+        <f>E20/Inputs!$E$11</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee B, % of TPV</t>
-        </is>
-      </c>
-      <c r="B24" s="36">
-        <f>B23/B17</f>
-        <v/>
-      </c>
-      <c r="C24" s="36">
-        <f>C23/C17</f>
-        <v/>
-      </c>
-      <c r="D24" s="36">
-        <f>D23/D17</f>
-        <v/>
-      </c>
-      <c r="E24" s="36">
-        <f>E23/E17</f>
+          <t xml:space="preserve">   Yuno usage only, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B24" s="42">
+        <f>B21/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C24" s="42">
+        <f>C21/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D24" s="42">
+        <f>D21/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E24" s="42">
+        <f>E21/Inputs!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee A a month</t>
+        </is>
+      </c>
+      <c r="B25" s="11">
+        <f>Inputs!$E$8*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="C25" s="11">
+        <f>Inputs!$E$9*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>Inputs!$E$10*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>Inputs!$E$11*Inputs!$E$40</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="63" t="inlineStr">
-        <is>
-          <t>Ticket $15</t>
-        </is>
-      </c>
-      <c r="B26" s="68">
-        <f>15</f>
-        <v/>
-      </c>
-      <c r="C26" s="67" t="n"/>
-      <c r="D26" s="67" t="n"/>
-      <c r="E26" s="67" t="n"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>B25/B19</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>C25/C19</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>D25/D19</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>E25/E19</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   TPV a month</t>
+          <t xml:space="preserve">   Fixed fee B a month</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>Inputs!$E$8*$B$26</f>
+        <f>Inputs!$E$8*Inputs!$E$41</f>
         <v/>
       </c>
       <c r="C27" s="11">
-        <f>Inputs!$E$9*$B$26</f>
+        <f>Inputs!$E$9*Inputs!$E$41</f>
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>Inputs!$E$10*$B$26</f>
+        <f>Inputs!$E$10*Inputs!$E$41</f>
         <v/>
       </c>
       <c r="E27" s="11">
-        <f>Inputs!$E$11*$B$26</f>
+        <f>Inputs!$E$11*Inputs!$E$41</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Yuno total a month</t>
-        </is>
-      </c>
-      <c r="B28" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(B27,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$8,Inputs!$E$34)*B27/Inputs!$E$8)))*Inputs!$E$36+MAX(0,MIN(B27,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$8,Inputs!$E$34)*B27/Inputs!$E$8)))*Inputs!$E$38+MAX(0,B27-MAX(Inputs!$E$37,(MIN(Inputs!$E$8,Inputs!$E$34)*B27/Inputs!$E$8)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="C28" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(C27,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$9,Inputs!$E$34)*C27/Inputs!$E$9)))*Inputs!$E$36+MAX(0,MIN(C27,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$9,Inputs!$E$34)*C27/Inputs!$E$9)))*Inputs!$E$38+MAX(0,C27-MAX(Inputs!$E$37,(MIN(Inputs!$E$9,Inputs!$E$34)*C27/Inputs!$E$9)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="D28" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(D27,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$10,Inputs!$E$34)*D27/Inputs!$E$10)))*Inputs!$E$36+MAX(0,MIN(D27,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$10,Inputs!$E$34)*D27/Inputs!$E$10)))*Inputs!$E$38+MAX(0,D27-MAX(Inputs!$E$37,(MIN(Inputs!$E$10,Inputs!$E$34)*D27/Inputs!$E$10)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f>Inputs!$E$33+MAX(0,MIN(E27,Inputs!$E$35)-MAX(0,(MIN(Inputs!$E$11,Inputs!$E$34)*E27/Inputs!$E$11)))*Inputs!$E$36+MAX(0,MIN(E27,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(Inputs!$E$11,Inputs!$E$34)*E27/Inputs!$E$11)))*Inputs!$E$38+MAX(0,E27-MAX(Inputs!$E$37,(MIN(Inputs!$E$11,Inputs!$E$34)*E27/Inputs!$E$11)))*Inputs!$E$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Yuno, % of TPV</t>
-        </is>
-      </c>
-      <c r="B29" s="48">
-        <f>B28/B27</f>
-        <v/>
-      </c>
-      <c r="C29" s="48">
-        <f>C28/C27</f>
-        <v/>
-      </c>
-      <c r="D29" s="48">
-        <f>D28/D27</f>
-        <v/>
-      </c>
-      <c r="E29" s="48">
-        <f>E28/E27</f>
+          <t xml:space="preserve">   Fixed fee B, % of TPV</t>
+        </is>
+      </c>
+      <c r="B28" s="36">
+        <f>B27/B19</f>
+        <v/>
+      </c>
+      <c r="C28" s="36">
+        <f>C27/C19</f>
+        <v/>
+      </c>
+      <c r="D28" s="36">
+        <f>D27/D19</f>
+        <v/>
+      </c>
+      <c r="E28" s="36">
+        <f>E27/E19</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Yuno, $ per transaction</t>
-        </is>
-      </c>
-      <c r="B30" s="42">
-        <f>B28/Inputs!$E$8</f>
-        <v/>
-      </c>
-      <c r="C30" s="42">
-        <f>C28/Inputs!$E$9</f>
-        <v/>
-      </c>
-      <c r="D30" s="42">
-        <f>D28/Inputs!$E$10</f>
-        <v/>
-      </c>
-      <c r="E30" s="42">
-        <f>E28/Inputs!$E$11</f>
-        <v/>
-      </c>
+      <c r="A30" s="63" t="inlineStr">
+        <is>
+          <t>Ticket $15</t>
+        </is>
+      </c>
+      <c r="B30" s="68">
+        <f>15</f>
+        <v/>
+      </c>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="67" t="n"/>
+      <c r="E30" s="67" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A a month</t>
+          <t xml:space="preserve">   Net TPV a month</t>
         </is>
       </c>
       <c r="B31" s="11">
-        <f>Inputs!$E$8*Inputs!$E$40</f>
+        <f>Inputs!$E$8*$B$30</f>
         <v/>
       </c>
       <c r="C31" s="11">
-        <f>Inputs!$E$9*Inputs!$E$40</f>
+        <f>Inputs!$E$9*$B$30</f>
         <v/>
       </c>
       <c r="D31" s="11">
-        <f>Inputs!$E$10*Inputs!$E$40</f>
+        <f>Inputs!$E$10*$B$30</f>
         <v/>
       </c>
       <c r="E31" s="11">
-        <f>Inputs!$E$11*Inputs!$E$40</f>
+        <f>Inputs!$E$11*$B$30</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
-        </is>
-      </c>
-      <c r="B32" s="36">
-        <f>B31/B27</f>
-        <v/>
-      </c>
-      <c r="C32" s="36">
-        <f>C31/C27</f>
-        <v/>
-      </c>
-      <c r="D32" s="36">
-        <f>D31/D27</f>
-        <v/>
-      </c>
-      <c r="E32" s="36">
-        <f>E31/E27</f>
+          <t xml:space="preserve">   Yuno total a month</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(B31,Inputs!$E$35)-MAX(0,(MIN(B31,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(B31,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(B31,Inputs!$E$34))))*Inputs!$E$38+MAX(0,B31-MAX(Inputs!$E$37,(MIN(B31,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(C31,Inputs!$E$35)-MAX(0,(MIN(C31,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(C31,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(C31,Inputs!$E$34))))*Inputs!$E$38+MAX(0,C31-MAX(Inputs!$E$37,(MIN(C31,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(D31,Inputs!$E$35)-MAX(0,(MIN(D31,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(D31,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(D31,Inputs!$E$34))))*Inputs!$E$38+MAX(0,D31-MAX(Inputs!$E$37,(MIN(D31,Inputs!$E$34))))*Inputs!$E$39</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>Inputs!$E$33+MAX(0,MIN(E31,Inputs!$E$35)-MAX(0,(MIN(E31,Inputs!$E$34))))*Inputs!$E$36+MAX(0,MIN(E31,Inputs!$E$37)-MAX(Inputs!$E$35,(MIN(E31,Inputs!$E$34))))*Inputs!$E$38+MAX(0,E31-MAX(Inputs!$E$37,(MIN(E31,Inputs!$E$34))))*Inputs!$E$39</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fixed fee B a month</t>
+          <t xml:space="preserve">   Yuno usage only</t>
         </is>
       </c>
       <c r="B33" s="11">
-        <f>Inputs!$E$8*Inputs!$E$41</f>
+        <f>B32-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="C33" s="11">
-        <f>Inputs!$E$9*Inputs!$E$41</f>
+        <f>C32-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="D33" s="11">
-        <f>Inputs!$E$10*Inputs!$E$41</f>
+        <f>D32-Inputs!$E$33</f>
         <v/>
       </c>
       <c r="E33" s="11">
-        <f>Inputs!$E$11*Inputs!$E$41</f>
+        <f>E32-Inputs!$E$33</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Yuno, % of TPV</t>
+        </is>
+      </c>
+      <c r="B34" s="51">
+        <f>B32/B31</f>
+        <v/>
+      </c>
+      <c r="C34" s="51">
+        <f>C32/C31</f>
+        <v/>
+      </c>
+      <c r="D34" s="51">
+        <f>D32/D31</f>
+        <v/>
+      </c>
+      <c r="E34" s="51">
+        <f>E32/E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yuno, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B35" s="42">
+        <f>B32/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C35" s="42">
+        <f>C32/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D35" s="42">
+        <f>D32/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E35" s="42">
+        <f>E32/Inputs!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yuno usage only, $ per transaction</t>
+        </is>
+      </c>
+      <c r="B36" s="42">
+        <f>B33/Inputs!$E$8</f>
+        <v/>
+      </c>
+      <c r="C36" s="42">
+        <f>C33/Inputs!$E$9</f>
+        <v/>
+      </c>
+      <c r="D36" s="42">
+        <f>D33/Inputs!$E$10</f>
+        <v/>
+      </c>
+      <c r="E36" s="42">
+        <f>E33/Inputs!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee A a month</t>
+        </is>
+      </c>
+      <c r="B37" s="11">
+        <f>Inputs!$E$8*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="C37" s="11">
+        <f>Inputs!$E$9*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="D37" s="11">
+        <f>Inputs!$E$10*Inputs!$E$40</f>
+        <v/>
+      </c>
+      <c r="E37" s="11">
+        <f>Inputs!$E$11*Inputs!$E$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee A, % of TPV</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>B37/B31</f>
+        <v/>
+      </c>
+      <c r="C38" s="36">
+        <f>C37/C31</f>
+        <v/>
+      </c>
+      <c r="D38" s="36">
+        <f>D37/D31</f>
+        <v/>
+      </c>
+      <c r="E38" s="36">
+        <f>E37/E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fixed fee B a month</t>
+        </is>
+      </c>
+      <c r="B39" s="11">
+        <f>Inputs!$E$8*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>Inputs!$E$9*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>Inputs!$E$10*Inputs!$E$41</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>Inputs!$E$11*Inputs!$E$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Fixed fee B, % of TPV</t>
         </is>
       </c>
-      <c r="B34" s="36">
-        <f>B33/B27</f>
-        <v/>
-      </c>
-      <c r="C34" s="36">
-        <f>C33/C27</f>
-        <v/>
-      </c>
-      <c r="D34" s="36">
-        <f>D33/D27</f>
-        <v/>
-      </c>
-      <c r="E34" s="36">
-        <f>E33/E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>B · Take rate on GMV: net benefit a month, base scenario (contribution view)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Take rate</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Net at tier 1</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Net at tier 4</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Net a year at tier 4</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Gross / Yuno at tier 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="69" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B38" s="16">
-        <f>Model!F28+(Model!F30+Model!F32)*($A38-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>Model!I28+(Model!I30+Model!I32)*($A38-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
-        <v/>
-      </c>
-      <c r="D38" s="11">
-        <f>C38*12</f>
-        <v/>
-      </c>
-      <c r="E38" s="20">
-        <f>(C38+Model!I21)/Model!I21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="70">
-        <f>Inputs!$E$13</f>
-        <v/>
-      </c>
-      <c r="B39" s="16">
-        <f>Model!F28+(Model!F30+Model!F32)*($A39-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>Model!I28+(Model!I30+Model!I32)*($A39-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>C39*12</f>
-        <v/>
-      </c>
-      <c r="E39" s="20">
-        <f>(C39+Model!I21)/Model!I21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="69" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="B40" s="16">
-        <f>Model!F28+(Model!F30+Model!F32)*($A40-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
-        <v/>
-      </c>
-      <c r="C40" s="16">
-        <f>Model!I28+(Model!I30+Model!I32)*($A40-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
-        <v/>
-      </c>
-      <c r="D40" s="11">
-        <f>C40*12</f>
-        <v/>
-      </c>
-      <c r="E40" s="20">
-        <f>(C40+Model!I21)/Model!I21</f>
+      <c r="B40" s="36">
+        <f>B39/B31</f>
+        <v/>
+      </c>
+      <c r="C40" s="36">
+        <f>C39/C31</f>
+        <v/>
+      </c>
+      <c r="D40" s="36">
+        <f>D39/D31</f>
+        <v/>
+      </c>
+      <c r="E40" s="36">
+        <f>E39/E31</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>C · Baseline provider cost: cost per $1,000 TPV and net benefit at tier 4, base scenario</t>
+          <t>B · Take rate on GMV: net benefit a month, base scenario (contribution view)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t>Take rate</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Net at tier 1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Net at tier 4</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Net a year at tier 4</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Gross / Yuno at tier 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B44" s="16">
+        <f>Model!F28+(Model!F30+Model!F32)*($A44-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
+        <v/>
+      </c>
+      <c r="C44" s="16">
+        <f>Model!I28+(Model!I30+Model!I32)*($A44-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
+        <v/>
+      </c>
+      <c r="D44" s="11">
+        <f>C44*12</f>
+        <v/>
+      </c>
+      <c r="E44" s="20">
+        <f>(C44+Model!I21)/Model!I21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="70">
+        <f>Inputs!$E$13</f>
+        <v/>
+      </c>
+      <c r="B45" s="16">
+        <f>Model!F28+(Model!F30+Model!F32)*($A45-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
+        <v/>
+      </c>
+      <c r="C45" s="16">
+        <f>Model!I28+(Model!I30+Model!I32)*($A45-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>C45*12</f>
+        <v/>
+      </c>
+      <c r="E45" s="20">
+        <f>(C45+Model!I21)/Model!I21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="69" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B46" s="16">
+        <f>Model!F28+(Model!F30+Model!F32)*($A46-Inputs!$E$14*Model!F26)+Model!F34-Model!F21</f>
+        <v/>
+      </c>
+      <c r="C46" s="16">
+        <f>Model!I28+(Model!I30+Model!I32)*($A46-Inputs!$E$14*Model!I26)+Model!I34-Model!I21</f>
+        <v/>
+      </c>
+      <c r="D46" s="11">
+        <f>C46*12</f>
+        <v/>
+      </c>
+      <c r="E46" s="20">
+        <f>(C46+Model!I21)/Model!I21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>C · Baseline provider cost: cost per $1,000 TPV and net benefit at tier 4, base scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>Baseline cost</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Option A $/1,000</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Option B $/1,000 (provider + Yuno)</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Option B $/1,000 after levers</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Net benefit a month</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Net a year</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="46">
+    <row r="50">
+      <c r="A50" s="45">
         <f>Inputs!$E$17</f>
         <v/>
       </c>
-      <c r="B44" s="13">
-        <f>$A44*1000</f>
-        <v/>
-      </c>
-      <c r="C44" s="13">
-        <f>(($A44-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
-        <v/>
-      </c>
-      <c r="D44" s="13">
-        <f>((($A44-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A44-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
-        <v/>
-      </c>
-      <c r="E44" s="16">
-        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A44-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
-        <v/>
-      </c>
-      <c r="F44" s="11">
-        <f>E44*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="46">
+      <c r="B50" s="13">
+        <f>$A50*1000</f>
+        <v/>
+      </c>
+      <c r="C50" s="13">
+        <f>(($A50-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
+        <v/>
+      </c>
+      <c r="D50" s="13">
+        <f>((($A50-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A50-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
+        <v/>
+      </c>
+      <c r="E50" s="16">
+        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A50-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
+        <v/>
+      </c>
+      <c r="F50" s="11">
+        <f>E50*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="45">
         <f>Inputs!$E$16</f>
         <v/>
       </c>
-      <c r="B45" s="13">
-        <f>$A45*1000</f>
-        <v/>
-      </c>
-      <c r="C45" s="13">
-        <f>(($A45-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
-        <v/>
-      </c>
-      <c r="D45" s="13">
-        <f>((($A45-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A45-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
-        <v/>
-      </c>
-      <c r="E45" s="16">
-        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A45-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
-        <v/>
-      </c>
-      <c r="F45" s="11">
-        <f>E45*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="46">
+      <c r="B51" s="13">
+        <f>$A51*1000</f>
+        <v/>
+      </c>
+      <c r="C51" s="13">
+        <f>(($A51-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
+        <v/>
+      </c>
+      <c r="D51" s="13">
+        <f>((($A51-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A51-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
+        <v/>
+      </c>
+      <c r="E51" s="16">
+        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A51-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>E51*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45">
         <f>Inputs!$E$18</f>
         <v/>
       </c>
-      <c r="B46" s="13">
-        <f>$A46*1000</f>
-        <v/>
-      </c>
-      <c r="C46" s="13">
-        <f>(($A46-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
-        <v/>
-      </c>
-      <c r="D46" s="13">
-        <f>((($A46-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A46-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
-        <v/>
-      </c>
-      <c r="E46" s="16">
-        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A46-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
-        <v/>
-      </c>
-      <c r="F46" s="11">
-        <f>E46*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="B52" s="13">
+        <f>$A52*1000</f>
+        <v/>
+      </c>
+      <c r="C52" s="13">
+        <f>(($A52-Inputs!$E$20/10000)+Model!I21/Model!I6)*1000</f>
+        <v/>
+      </c>
+      <c r="D52" s="13">
+        <f>((($A52-Inputs!$E$20/10000)+Model!I21/Model!I6)*Model!I6-((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A52-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34))/Model!I6*1000</f>
+        <v/>
+      </c>
+      <c r="E52" s="16">
+        <f>Model!I28+((Model!I30+Model!I32)*(Inputs!$E$13-Inputs!$E$14*(($A52-Inputs!$E$20/10000)+Model!I21/Model!I6))+Model!I34)-Model!I21</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>E52*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>L1 (MDR reduction in bps) does not move with the baseline: the saving is the gap between the two routes, not the level. The baseline changes the all-in cost of both options and, through netting, the contribution on incremental GMV.</t>
         </is>
@@ -15653,8 +15976,8 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A36:J36"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A48:J48"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>
   </mergeCells>
@@ -15740,12 +16063,12 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>Justo Benetti (Yuno CRO), brief for the business case, 15 Oct 2026</t>
+          <t>Justo Benetti (Yuno CRO) and German Tatis, pricing v3 and business-case brief, 15 Oct 2026</t>
         </is>
       </c>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>$7,500 a month platform commitment with a block of transactions included; usage as % of TPV; levers MDR 25/50/75 bps; numbers tied to a low transaction count.</t>
+          <t>$7,500 a month flat platform fee including the first block of monthly Net TPV; usage in bps on Net TPV above it, ladder 30 / 25 / 20 bps; levers MDR 25/50/75 bps; numbers tied to a low transaction count.</t>
         </is>
       </c>
       <c r="D6" s="28" t="inlineStr">
@@ -15965,7 +16288,7 @@
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>7% authorization uplift; 30% recovered revenue. Used only as the ceiling for the optimistic approval case.</t>
+          <t>7% authorization uplift; 30% recovered revenue; 1,000+ payment methods, PSPs and fraud solutions. The 7% is used only as the ceiling for the optimistic approval case.</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BreakEven" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ramp" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TimeToMarket" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1146,22 +1147,179 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>How to read: Option A = EBANX direct at the baseline all-in cost (ESTIMATE until EBANX's quote replaces the baseline on Inputs). Option B = EBANX primary + dLocal second MoR through Yuno; its provider cost is the baseline minus the MDR reduction, plus Yuno's flat platform fee and usage in bps on the Net TPV above the included block. Levers: L1 MDR saving (100% contribution), L2 retries and routing, L3 local methods, L4 integrations avoided (per-market EBANX work, later direct integrations, maintenance; deck lever L2). Contribution view nets the take rate and processing cost on incremental GMV. Yuno-wide figures used only as guardrails: 7% authorization uplift, 30% recovered revenue (y.uno).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Time to market (L5, deck L3): 2027 value, kept apart</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Through Yuno: run-rate month</t>
+        </is>
+      </c>
+      <c r="D29" s="22">
+        <f>TimeToMarket!B23</f>
+        <v/>
+      </c>
+      <c r="E29" s="22">
+        <f>TimeToMarket!C23</f>
+        <v/>
+      </c>
+      <c r="F29" s="22">
+        <f>TimeToMarket!D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Extra sales in 2027</t>
+        </is>
+      </c>
+      <c r="D30" s="11">
+        <f>TimeToMarket!B24</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>TimeToMarket!C24</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
+        <f>TimeToMarket!D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>L5 · 2027 value from reaching run rate sooner</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>TimeToMarket!B27</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>TimeToMarket!C27</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>TimeToMarket!D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Recurring levers a year at run rate</t>
+        </is>
+      </c>
+      <c r="D32" s="11">
+        <f>TimeToMarket!B28</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>TimeToMarket!C28</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>TimeToMarket!D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>2027 value including time to market</t>
+        </is>
+      </c>
+      <c r="D33" s="16">
+        <f>TimeToMarket!B29</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f>TimeToMarket!C29</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f>TimeToMarket!D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Net 2027 including time to market</t>
+        </is>
+      </c>
+      <c r="D34" s="16">
+        <f>TimeToMarket!B32</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>TimeToMarket!C32</f>
+        <v/>
+      </c>
+      <c r="F34" s="16">
+        <f>TimeToMarket!D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2027 value / Yuno cost</t>
+        </is>
+      </c>
+      <c r="D35" s="20">
+        <f>TimeToMarket!B34</f>
+        <v/>
+      </c>
+      <c r="E35" s="20">
+        <f>TimeToMarket!C34</f>
+        <v/>
+      </c>
+      <c r="F35" s="20">
+        <f>TimeToMarket!D34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>How to read: Option A = EBANX direct at the baseline all-in cost (ESTIMATE until EBANX's quote replaces the baseline on Inputs). Option B = EBANX primary + dLocal second MoR through Yuno; its provider cost is the baseline minus the MDR reduction, plus Yuno's flat platform fee and usage in bps on the Net TPV above the included block. Levers: L1 MDR saving (100% contribution), L2 retries and routing, L3 local methods, L4 integrations avoided (per-market EBANX work, later direct integrations, maintenance; deck lever L5), and, kept apart as a 2027 value, L5 time to market (run rate reached by mid 2027 instead of end 2027; deck lever L3). Contribution view nets the take rate and processing cost on incremental GMV. Yuno-wide figures used only as guardrails: 7% authorization uplift, 30% recovered revenue (y.uno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="30">
+    <mergeCell ref="B37:G40"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B12:C12"/>
@@ -1172,14 +1330,20 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B28:G31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1191,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1805,17 +1969,17 @@
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="E25" s="31" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F25" s="31" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>ESTIMATE. Methods carried through Yuno via dLocal and not on the EBANX connection (docs.y.uno Payment Type list, 14 Oct 2026): Argentina MODO, Rapipago, Pago Facil; Colombia Bre-B, Nequi, PSE, Efecty; Bolivia Multipago, Pago al Paso; Mexico CoDi, Paynet, 7-Eleven. Context: Pix = 42% of Brazil e-commerce value in 2025 (Worldpay GPR 2026 via Poder360); account-to-account 15% and wallets 39% of Argentina e-commerce value 2025 (GPR 2026 via LetsMoney); QR = 36% of payments in Bolivia in 2025 (Banco Central de Bolivia via Los Tiempos, Jun 2026). EBANX direct coverage per country TO VALIDATE against its quote.</t>
+          <t>ESTIMATE, +2 / +4 / +6% of sales (German, 15 Oct 2026: LatAm is APM-driven). Basis: Pix is 42% of online purchases in Brazil, PSE 64% of e-commerce transactions in Colombia, wallets 46% of e-commerce in Argentina (German, 15 Oct 2026). Through Yuno the checkout adds the methods a single provider does not carry (MODO and interoperable QR in Argentina, Bre-B and Nequi in Colombia, cards and QR in Bolivia) and optimizes the method mix per market. Methods carried through Yuno via dLocal and not on the EBANX connection (docs.y.uno Payment Type list, 14 Oct 2026): Argentina MODO, Rapipago, Pago Facil; Colombia Bre-B, Nequi, PSE, Efecty; Bolivia Multipago, Pago al Paso; Mexico CoDi, Paynet, 7-Eleven. Context: Pix = 42% of Brazil e-commerce value in 2025 (Worldpay GPR 2026 via Poder360); account-to-account 15% and wallets 39% of Argentina e-commerce value 2025 (GPR 2026 via LetsMoney); QR = 36% of payments in Bolivia in 2025 (Banco Central de Bolivia via Los Tiempos, Jun 2026). EBANX direct coverage per country TO VALIDATE against its quote.</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
@@ -1827,7 +1991,7 @@
     <row r="26">
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>6 · Lever 4 (deck L2) · Integrations avoided: per-market EBANX work, later direct integrations, maintenance</t>
+          <t>6 · Lever 4 (deck L5) · Integrations avoided: per-market EBANX work, later direct integrations, maintenance</t>
         </is>
       </c>
       <c r="C26" s="25" t="n"/>
@@ -2502,7 +2666,7 @@
     <row r="49">
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>9 · INTERNAL launch lever (switch, default 0 = off; delete this section before the file leaves Yuno)</t>
+          <t>9 · Lever 5 (deck L3) · Time to market: run rate reached sooner (2027 value, kept apart from the recurring levers)</t>
         </is>
       </c>
       <c r="C49" s="25" t="n"/>
@@ -2512,85 +2676,63 @@
       <c r="G49" s="25" t="n"/>
       <c r="H49" s="25" t="n"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="45" customHeight="1">
       <c r="B50" s="10" t="inlineStr">
         <is>
+          <t>Through Yuno: months after Dec 2026 to reach the run rate (9 = Sep 2027, 6 = Jun 2027, 4 = Apr 2027), then flat</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" s="28" t="inlineStr">
+        <is>
+          <t>Yuno estimate. Through Yuno all five markets go live together on one integration, each with its local methods and more than one provider, so the Shop reaches Cordel's $4 to 5M a month (modelled $4.5M) by mid 2027. Going direct with EBANX, markets are enabled one by one, so the ramp runs linearly from tier 1 in Dec 2026 to tier 4 in Dec 2027 (the ramp months above). Value = extra GMV in 2027 x (take rate minus Option B all-in processing % at run rate). A one-off 2027 value, never added to the recurring a-year totals.</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="inlineStr">
+        <is>
+          <t>Cordel (volumes by country) · Fatih (launch scope)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>10 · INTERNAL launch lever (switch, default 0 = off; delete this section before the file leaves Yuno)</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="10" t="inlineStr">
+        <is>
           <t>Launch credit switch (1 = on, 0 = off)</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
       </c>
-      <c r="D50" s="33" t="n">
+      <c r="D52" s="33" t="n">
         <v>0</v>
-      </c>
-      <c r="E50" s="34">
-        <f>D50</f>
-        <v/>
-      </c>
-      <c r="F50" s="34">
-        <f>D50</f>
-        <v/>
-      </c>
-      <c r="G50" s="28" t="inlineStr">
-        <is>
-          <t>INTERNAL. Optional lever: a monthly credit against the platform fee for the first months after the 1 Dec 2026 billing start. Applies on the Ramp sheet only. Never on the customer slide.</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="inlineStr">
-        <is>
-          <t>Justo · Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>Monthly credit against the platform fee when the switch is on</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D51" s="41" t="n">
-        <v>3750</v>
-      </c>
-      <c r="E51" s="11">
-        <f>D51</f>
-        <v/>
-      </c>
-      <c r="F51" s="11">
-        <f>D51</f>
-        <v/>
-      </c>
-      <c r="G51" s="28" t="inlineStr">
-        <is>
-          <t>INTERNAL. Credits are allowed against the platform fee only, for named months, written in the contract, no rollover.</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="inlineStr">
-        <is>
-          <t>Justo · Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Months the credit applies (from the billing start)</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D52" s="33" t="n">
-        <v>3</v>
       </c>
       <c r="E52" s="34">
         <f>D52</f>
@@ -2602,24 +2744,90 @@
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
+          <t>INTERNAL. Optional lever: a monthly credit against the platform fee for the first months after the 1 Dec 2026 billing start. Applies on the Ramp sheet only. Never on the customer slide.</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="inlineStr">
+        <is>
+          <t>Justo · Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Monthly credit against the platform fee when the switch is on</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E53" s="11">
+        <f>D53</f>
+        <v/>
+      </c>
+      <c r="F53" s="11">
+        <f>D53</f>
+        <v/>
+      </c>
+      <c r="G53" s="28" t="inlineStr">
+        <is>
+          <t>INTERNAL. Credits are allowed against the platform fee only, for named months, written in the contract, no rollover.</t>
+        </is>
+      </c>
+      <c r="H53" s="28" t="inlineStr">
+        <is>
+          <t>Justo · Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Months the credit applies (from the billing start)</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D54" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="34">
+        <f>D54</f>
+        <v/>
+      </c>
+      <c r="F54" s="34">
+        <f>D54</f>
+        <v/>
+      </c>
+      <c r="G54" s="28" t="inlineStr">
+        <is>
           <t>INTERNAL. Dec 2026 to Feb 2027.</t>
         </is>
       </c>
-      <c r="H52" s="28" t="inlineStr">
+      <c r="H54" s="28" t="inlineStr">
         <is>
           <t>Justo · Finance</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="44" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="44" t="inlineStr">
         <is>
           <t>Published Yuno figures used as guardrails only (never as inputs): 7% authorization uplift and 30% recovered revenue (y.uno). Treat 7% as the ceiling for the optimistic case.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="44" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="44" t="inlineStr">
         <is>
           <t>Labels: CONFIRMED (docs.y.uno or y.uno) · PUBLIC DOCS (third-party page, dated) · OPEN (not confirmed in writing, with owner) · ESTIMATE (modeled; assumption stated) · Carry1st estimate (Cordel, Oct 2026).</t>
         </is>
@@ -5429,7 +5637,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>L4 (deck L2) · integrations avoided: per-market EBANX work and later integrations over the horizon, plus maintenance, monthly</t>
+          <t>L4 (deck L5) · integrations avoided: per-market EBANX work and later integrations over the horizon, plus maintenance, monthly</t>
         </is>
       </c>
       <c r="B35" s="11">
@@ -13940,7 +14148,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Payback month = first month in which the cumulative net benefit (contribution view) is non-negative. The INTERNAL launch credit switch (Inputs section 9) applies on this sheet only; default off.</t>
+          <t>Payback month = first month in which the cumulative net benefit (contribution view) is non-negative. The INTERNAL launch credit switch (Inputs section 10) applies on this sheet only; default off.</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14385,7 @@
         <v/>
       </c>
       <c r="D12" s="57">
-        <f>IF(AND(Inputs!$E$50=1,1&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,1&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E12" s="57">
@@ -14256,7 +14464,7 @@
         <v/>
       </c>
       <c r="D13" s="57">
-        <f>IF(AND(Inputs!$E$50=1,2&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,2&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E13" s="57">
@@ -14335,7 +14543,7 @@
         <v/>
       </c>
       <c r="D14" s="57">
-        <f>IF(AND(Inputs!$E$50=1,3&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,3&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E14" s="57">
@@ -14414,7 +14622,7 @@
         <v/>
       </c>
       <c r="D15" s="57">
-        <f>IF(AND(Inputs!$E$50=1,4&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,4&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E15" s="57">
@@ -14493,7 +14701,7 @@
         <v/>
       </c>
       <c r="D16" s="57">
-        <f>IF(AND(Inputs!$E$50=1,5&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,5&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E16" s="57">
@@ -14572,7 +14780,7 @@
         <v/>
       </c>
       <c r="D17" s="57">
-        <f>IF(AND(Inputs!$E$50=1,6&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,6&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E17" s="57">
@@ -14651,7 +14859,7 @@
         <v/>
       </c>
       <c r="D18" s="57">
-        <f>IF(AND(Inputs!$E$50=1,7&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,7&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E18" s="57">
@@ -14730,7 +14938,7 @@
         <v/>
       </c>
       <c r="D19" s="57">
-        <f>IF(AND(Inputs!$E$50=1,8&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,8&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E19" s="57">
@@ -14809,7 +15017,7 @@
         <v/>
       </c>
       <c r="D20" s="57">
-        <f>IF(AND(Inputs!$E$50=1,9&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,9&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E20" s="57">
@@ -14888,7 +15096,7 @@
         <v/>
       </c>
       <c r="D21" s="57">
-        <f>IF(AND(Inputs!$E$50=1,10&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,10&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E21" s="57">
@@ -14967,7 +15175,7 @@
         <v/>
       </c>
       <c r="D22" s="57">
-        <f>IF(AND(Inputs!$E$50=1,11&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,11&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E22" s="57">
@@ -15046,7 +15254,7 @@
         <v/>
       </c>
       <c r="D23" s="57">
-        <f>IF(AND(Inputs!$E$50=1,12&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,12&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E23" s="57">
@@ -15125,7 +15333,7 @@
         <v/>
       </c>
       <c r="D24" s="57">
-        <f>IF(AND(Inputs!$E$50=1,13&lt;=Inputs!$E$52),Inputs!$E$51,0)</f>
+        <f>IF(AND(Inputs!$E$52=1,13&lt;=Inputs!$E$54),Inputs!$E$53,0)</f>
         <v/>
       </c>
       <c r="E24" s="57">
@@ -15267,6 +15475,906 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time to market · going direct (markets enabled one by one, run rate in Dec 2027) vs through Yuno (all five markets live together, run rate by mid 2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Monthly sales (Net TPV). Direct: linear from tier 1 in Dec 2026 to tier 4 in Dec 2027. Yuno: linear from tier 1 to tier 4 by the run-rate month on Inputs, then flat. Value = extra 2027 sales x (take rate minus Option B all-in % at run rate). One-off 2027 value, kept apart from the recurring levers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="9.75" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Months after Dec 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Going direct, sales</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Through Yuno, sales</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Extra sales</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Through Yuno, sales</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Extra sales</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Through Yuno, sales</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Extra sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B7/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D7" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B7,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E7" s="59">
+        <f>D7-C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B7,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G7" s="59">
+        <f>F7-C7</f>
+        <v/>
+      </c>
+      <c r="H7" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B7,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I7" s="59">
+        <f>H7-C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Jan 2027</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B8/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D8" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B8,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E8" s="59">
+        <f>D8-C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B8,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G8" s="59">
+        <f>F8-C8</f>
+        <v/>
+      </c>
+      <c r="H8" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B8,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I8" s="59">
+        <f>H8-C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B9/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D9" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B9,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E9" s="59">
+        <f>D9-C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B9,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G9" s="59">
+        <f>F9-C9</f>
+        <v/>
+      </c>
+      <c r="H9" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B9,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I9" s="59">
+        <f>H9-C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B10/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D10" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B10,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E10" s="59">
+        <f>D10-C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B10,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G10" s="59">
+        <f>F10-C10</f>
+        <v/>
+      </c>
+      <c r="H10" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B10,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I10" s="59">
+        <f>H10-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B11/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D11" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B11,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E11" s="59">
+        <f>D11-C11</f>
+        <v/>
+      </c>
+      <c r="F11" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B11,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G11" s="59">
+        <f>F11-C11</f>
+        <v/>
+      </c>
+      <c r="H11" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B11,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I11" s="59">
+        <f>H11-C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B12/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D12" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B12,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E12" s="59">
+        <f>D12-C12</f>
+        <v/>
+      </c>
+      <c r="F12" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B12,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G12" s="59">
+        <f>F12-C12</f>
+        <v/>
+      </c>
+      <c r="H12" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B12,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I12" s="59">
+        <f>H12-C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B13/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D13" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B13,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E13" s="59">
+        <f>D13-C13</f>
+        <v/>
+      </c>
+      <c r="F13" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B13,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G13" s="59">
+        <f>F13-C13</f>
+        <v/>
+      </c>
+      <c r="H13" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B13,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I13" s="59">
+        <f>H13-C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B14/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D14" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B14,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E14" s="59">
+        <f>D14-C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B14,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G14" s="59">
+        <f>F14-C14</f>
+        <v/>
+      </c>
+      <c r="H14" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B14,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I14" s="59">
+        <f>H14-C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Aug 2027</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B15/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B15,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E15" s="59">
+        <f>D15-C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B15,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G15" s="59">
+        <f>F15-C15</f>
+        <v/>
+      </c>
+      <c r="H15" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B15,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I15" s="59">
+        <f>H15-C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Sep 2027</t>
+        </is>
+      </c>
+      <c r="B16" s="60" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B16/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D16" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B16,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E16" s="59">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B16,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G16" s="59">
+        <f>F16-C16</f>
+        <v/>
+      </c>
+      <c r="H16" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B16,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I16" s="59">
+        <f>H16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="B17" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B17/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D17" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B17,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E17" s="59">
+        <f>D17-C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B17,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G17" s="59">
+        <f>F17-C17</f>
+        <v/>
+      </c>
+      <c r="H17" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B17,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I17" s="59">
+        <f>H17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Nov 2027</t>
+        </is>
+      </c>
+      <c r="B18" s="60" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B18/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D18" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B18,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E18" s="59">
+        <f>D18-C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B18,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G18" s="59">
+        <f>F18-C18</f>
+        <v/>
+      </c>
+      <c r="H18" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B18,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I18" s="59">
+        <f>H18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Dec 2027</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*B19/(Inputs!$E$48-1)</f>
+        <v/>
+      </c>
+      <c r="D19" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B19,Inputs!$D$50)/Inputs!$D$50</f>
+        <v/>
+      </c>
+      <c r="E19" s="59">
+        <f>D19-C19</f>
+        <v/>
+      </c>
+      <c r="F19" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B19,Inputs!$E$50)/Inputs!$E$50</f>
+        <v/>
+      </c>
+      <c r="G19" s="59">
+        <f>F19-C19</f>
+        <v/>
+      </c>
+      <c r="H19" s="57">
+        <f>Inputs!$E$8*Inputs!$E$6+(Inputs!$E$11*Inputs!$E$6-Inputs!$E$8*Inputs!$E$6)*MIN(B19,Inputs!$F$50)/Inputs!$F$50</f>
+        <v/>
+      </c>
+      <c r="I19" s="59">
+        <f>H19-C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="inlineStr">
+        <is>
+          <t>Total 2027 (Jan to Dec)</t>
+        </is>
+      </c>
+      <c r="C20" s="65">
+        <f>SUM(C8:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="65">
+        <f>SUM(D8:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="65">
+        <f>SUM(E8:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="65">
+        <f>SUM(F8:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="65">
+        <f>SUM(G8:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="65">
+        <f>SUM(H8:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="65">
+        <f>SUM(I8:I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Through Yuno: run-rate month</t>
+        </is>
+      </c>
+      <c r="B23" s="22">
+        <f>INDEX($A$7:$A$19,Inputs!$D$50+1)</f>
+        <v/>
+      </c>
+      <c r="C23" s="22">
+        <f>INDEX($A$7:$A$19,Inputs!$E$50+1)</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>INDEX($A$7:$A$19,Inputs!$F$50+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Extra sales in 2027 (GMV)</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>E20</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>I20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Option B all-in processing, % of sales at run rate</t>
+        </is>
+      </c>
+      <c r="B25" s="46">
+        <f>Model!E27</f>
+        <v/>
+      </c>
+      <c r="C25" s="46">
+        <f>Model!I27</f>
+        <v/>
+      </c>
+      <c r="D25" s="46">
+        <f>Model!M27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Contribution per $1 of extra sales (take rate minus processing)</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>Inputs!$D$13-Inputs!$D$14*B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Inputs!$E$13-Inputs!$E$14*C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Inputs!$F$13-Inputs!$F$14*D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>L5 (deck L3) · time to market, 2027 value from reaching run rate sooner</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>B24*B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>C24*C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>D24*D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Recurring levers L1 to L4, a year at run rate (gross, contribution)</t>
+        </is>
+      </c>
+      <c r="B28" s="45">
+        <f>Model!E47</f>
+        <v/>
+      </c>
+      <c r="C28" s="45">
+        <f>Model!I47</f>
+        <v/>
+      </c>
+      <c r="D28" s="45">
+        <f>Model!M47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2027 value including time to market (recurring + L5)</t>
+        </is>
+      </c>
+      <c r="B29" s="16">
+        <f>B28+B27</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>C28+C27</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>D28+D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Yuno cost a year at run rate</t>
+        </is>
+      </c>
+      <c r="B30" s="45">
+        <f>Model!E46</f>
+        <v/>
+      </c>
+      <c r="C30" s="45">
+        <f>Model!I46</f>
+        <v/>
+      </c>
+      <c r="D30" s="45">
+        <f>Model!M46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Net a year, recurring levers only</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>B28-B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>C28-C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>D28-D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Net, 2027 value including time to market</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>B29-B30</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>C29-C30</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>D29-D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Recurring levers / Yuno cost</t>
+        </is>
+      </c>
+      <c r="B33" s="20">
+        <f>B28/B30</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>C28/C30</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
+        <f>D28/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2027 value including time to market / Yuno cost</t>
+        </is>
+      </c>
+      <c r="B34" s="20">
+        <f>B29/B30</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f>C29/C30</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f>D29/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>L5 is value in the first year from reaching scale sooner: shown as a 2027 figure and never added to the recurring a-year totals. Ramp shapes are Yuno ESTIMATES; replace with Cordel's written projections by country.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16293,7 +17401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="D28" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="28" t="inlineStr">
         <is>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="28" t="inlineStr">
         <is>
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="D30" s="38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G30" s="28" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="D31" s="39" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E31" s="11">
         <f>D31</f>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>ESTIMATE, about $104K a year loaded. Sits between Cape Town senior engineer market pay (PayScale, 2026; Carry1st engineers are in Cape Town) and LatAm loaded cost of $87.5K to $100.8K a year (Second Talent, 2026); US fully loaded is $200K to $280K (Revelo, 2026).</t>
+          <t>ESTIMATE, $130K a year loaded: a senior payments engineer (Justo, 15 Oct 2026: incremental dev cost avoided above $150K a year). Above LatAm loaded cost of $87.5K to $100.8K a year (Second Talent, 2026), below US fully loaded $200K to $280K (Revelo, 2026).</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
@@ -2172,13 +2172,13 @@
         </is>
       </c>
       <c r="D32" s="40" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E32" s="40" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F32" s="40" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G32" s="28" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>52 weeks x $2,000 = $104K a year loaded per FTE.</t>
+          <t>52 weeks x $2,500 = $130K a year loaded per FTE.</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr"/>

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -2694,7 +2694,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50" s="38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50" s="38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>

--- a/Deals/Carry1st/build/model/bc_model.xlsx
+++ b/Deals/Carry1st/build/model/bc_model.xlsx
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="D50" s="38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E50" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="F50" s="38" t="n">
         <v>8</v>
-      </c>
-      <c r="F50" s="38" t="n">
-        <v>7</v>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>
